--- a/untitled folder/HSC_Physics_1st_Paper_Chapter_10_Ideal_Gas_and_Kinetic_Theory_of_Gases.xlsx
+++ b/untitled folder/HSC_Physics_1st_Paper_Chapter_10_Ideal_Gas_and_Kinetic_Theory_of_Gases.xlsx
@@ -1168,11 +1168,6 @@
           <t>একটি হ্রদের তলদেশ থেকে নির্গত একটি বায়ু বুদ্বুদ পানির উপরিভাগে পৌঁছালে তার আয়তন $8$ গুণ বৃদ্ধি পায়। হ্রদের তলদেশের তাপমাত্রা $7^\circ\text{C}$ এবং পানির পৃষ্ঠের তাপমাত্রা $27^\circ\text{C}$। বায়ুমণ্ডলীয় চাপ $P_0 = 10^5\text{ Pa}$ এবং পানির ঘনত্ব $\rho = 1000\text{ kg m}^{-3}$ হলে হ্রদের গভীরতা $h$ নির্ণয় করো। পানির পৃষ্ঠটানের প্রভাব আলোচনা করো। [$g = 9.8\text{ m s}^{-2}$]</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>হ্রদের তলদেশ থেকে বুদ্বুদের আরোহণ ও বয়েল-চার্লসের যৌথ সূত্র:</t>
@@ -1218,11 +1213,6 @@
           <t>সমোষ্ণ বায়ুমণ্ডলে উচ্চতা $z$-এর সাথে চাপের হ্রাস নির্দেশকারী ব্যারোমেট্রিক সূত্র $P(z) = P_0 e^{-\frac{M g z}{R T}}$ প্রতিপাদন করো। সমুদ্রপৃষ্ঠ থেকে কত উচ্চতায় বাতাসের চাপ প্রমাণ বায়ুমণ্ডলীয় চাপের ঠিক অর্ধেক হবে? [বাতাসের গড় আণবিক ভর $M = 29\text{ g mol}^{-1}$, $T = 290\text{ K}$, $g = 9.8\text{ m s}^{-2}$, $R = 8.314\text{ J mol}^{-1}\text{ K}^{-1}$]</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>ব্যারোমেট্রিক সূত্রের ব্যবকলনীয় প্রতিপাদন ও অর্ধ-উচ্চতা গণনা:</t>
@@ -1268,11 +1258,6 @@
           <t>ডাল্টনের আংশিক চাপ নীতি কী? একটি $V = 20\text{ L}$ আয়তনের পাত্রে $27^\circ\text{C}$ তাপমাত্রায় $m_1 = 16\text{ g}$ অক্সিজেন ($\text{O}_2$), $m_2 = 14\text{ g}$ নাইট্রোজেন ($\text{N}_2$) এবং $m_3 = 11\text{ g}$ কার্বন ডাই অক্সাইড ($\text{CO}_2$) গ্যাস রাখা হলো। পাত্রটিতে প্রতিটি গ্যাসের আংশিক চাপ এবং মোট চাপ নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>ডাল্টনের আংশিক চাপ নীতি ও মিশ্রণের মোট চাপ গণনা:</t>
@@ -1318,11 +1303,6 @@
           <t>গ্রাহামের গ্যাস ব্যাপন সূত্র (Graham's Law of Diffusion) প্রতিপাদন করো। ইউরেনিয়াম সমৃদ্ধকরণে $^{235}\text{UF}_6$ এবং $^{238}\text{UF}_6$ গ্যাসীয় যৌগের ব্যাপন হারের আপেক্ষিক অনুপাত নির্ণয় করো। গ্যাসীয় সেন্ট্রিফিউজ পদ্ধতি উদ্ভাবনের পূর্বে কেন বহু-ধাপ বিশিষ্ট ব্যাপন ব্যবস্থার প্রয়োজন হতো? [$^{235}\text{U} = 235$, $^{238}\text{U} = 238$, $^{19}\text{F} = 19$]</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>গ্রাহামের ব্যাপন সূত্র ও আইসোটোপীয় পৃথকীকরণ দক্ষতা:</t>
@@ -1368,11 +1348,6 @@
           <t>$V_1$ আয়তন ও $P_1$ চাপের একটি পাত্র এবং $V_2$ আয়তন ও $P_2$ চাপের অপর একটি পাত্র একটি সরু স্টপকক নল দ্বারা যুক্ত। সমগ্র ব্যবস্থাটি একই তাপমাত্রা $T$-এ স্থির রাখা হলো। স্টপকক খুলে দিলে গ্যাস দুটি মিশ্রিত হয়ে চূড়ান্ত সাম্যাবস্থা লাভ করে। মিশ্রণের চূড়ান্ত চাপ $P_{\text{final}} = \frac{P_1 V_1 + P_2 V_2}{V_1 + V_2}$ প্রতিপাদন করো। তাপমাত্রা যদি যথাক্রমে $T_1$ ও $T_2$ এবং চূড়ান্ত তাপমাত্রা $T_f$ হতো, তবে চাপের রূপ কেমন হতো?</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>সংযুক্ত পাত্রে গ্যাস মিশ্রণের চূড়ান্ত চাপ প্রতিপাদন:</t>
@@ -1418,11 +1393,6 @@
           <t>একটি গ্যাস সিলিন্ডারে $300\text{ K}$ তাপমাত্রায় $20\text{ atm}$ চাপে অক্সিজেন সংরক্ষিত আছে। হঠাৎ সিলিন্ডারের নিরাপত্তা ভাল্ব লিক হওয়ায় কিছু গ্যাস বেরিয়ে যায় এবং চাপ কমে $15\text{ atm}$-এ নেমে আসে। তাপমাত্রা যদি অপরিবর্তিত থাকে, তবে সিলিন্ডার থেকে কত ভগ্নাংশ গ্যাস বেরিয়ে গেছে? যদি সিলিন্ডারটির আয়তন $50\text{ L}$ হয়, তবে নির্গত গ্যাসের ভর কত?</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>সিলিন্ডার লিকেজে গ্যাসের ভগ্নাংশ ও নির্গত ভর গণনা:</t>
@@ -1468,11 +1438,6 @@
           <t>একটি ত্রুটিপূর্ণ ব্যারোমিটারের কাঁচের নলের পারদ স্তম্ভের ওপরে সামান্য বাতাস আটকে আছে। যখন প্রকৃত বায়ুমণ্ডলীয় চাপ $76\text{ cm-Hg}$, তখন ব্যারোমিটারের পাঠ $74\text{ cm-Hg}$ এবং পারদের ওপরে ফাঁকা নলের দৈর্ঘ্য $10\text{ cm}$। যখন ব্যারোমিটারের পাঠ $72\text{ cm-Hg}$ নির্দেশ করে, তখন প্রকৃত বায়ুমণ্ডলীয় চাপ কত ছিল? [নলের তাপমাত্রা স্থির]</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>ত্রুটিপূর্ণ ব্যারোমিটারে আবদ্ধ বাতাসের বয়েল সূত্র প্রয়োগ:</t>
@@ -1518,11 +1483,6 @@
           <t>একটি দীর্ঘ উলম্ব কাঁচের নলের এক প্রান্ত বন্ধ এবং অপর প্রান্ত খোলা। নলে $h = 15\text{ cm}$ দৈর্ঘ্যের একটি পারদ সুতো দ্বারা $l = 30\text{ cm}$ দৈর্ঘ্যের বাতাস কলাম আটকে রাখা আছে। বায়ুমণ্ডলীয় চাপ $P_0 = 75\text{ cm-Hg}$। নলটিকে ধীরে ধীরে ঘুরিয়ে সম্পূর্ণ উল্টো (খোলা মুখ নিচে) করলে আটকে থাকা বাতাস কলামের নতুন দৈর্ঘ্য কত হবে?</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>উল্টানো নলে পারদ সুতো ও আবদ্ধ বাতাসের ভারসাম্য:</t>
@@ -1568,11 +1528,6 @@
           <t>একটি আবহাওয়া বেলুনের আয়তন $V = 100\text{ m}^3$ এবং তা $1\text{ atm}$ ও $27^\circ\text{C}$-এ হিলিয়াম গ্যাস দ্বারা পূর্ণ। বায়ুমণ্ডলে বেলুনটির মোট বহন ক্ষমতা (payload capacity) কত? [বাতাসের গড় ঘনত্ব $\rho_{\text{air}} = 1.20\text{ kg m}^{-3}$, হিলিয়ামের ঘনত্ব $\rho_{\text{He}} = 0.16\text{ kg m}^{-3}$, বেলুনের খোলসের ভর $M_{\text{balloon}} = 15\text{ kg}$]</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>আর্কিমিডিসের প্লাবতা ও বেলুনের পেলোড গণনা:</t>
@@ -1618,11 +1573,6 @@
           <t>একটি তাপ নিরোধক সিলিন্ডার একটি ঘর্ষণহীন পরিবাহী পিস্টন দ্বারা দুটি সমান আয়তন $V_0$-তে বিভক্ত। বাম প্রকোষ্ঠে $T_0$ তাপমাত্রায় $P_1$ চাপের গ্যাস এবং ডান প্রকোষ্ঠে একই তাপমাত্রায় $P_2$ চাপের গ্যাস আছে ($P_1 &gt; P_2$)। পিস্টনটিকে মুক্ত করে দিলে এটি সাম্যাবস্থায় পৌঁছায়। পিস্টনের চূড়ান্ত অবস্থান এবং চূড়ান্ত সাম্য চাপ নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>পরিবাহী পিস্টন দ্বারা বিভক্ত প্রকোষ্ঠের যান্ত্রিক সাম্যাবস্থা:</t>
@@ -1668,11 +1618,6 @@
           <t>গ্যাসের গতিতত্ত্বের মৌলিক স্বীকার্যসমূহ কী কী? আদর্শ গ্যাসের গতীয় সমীকরণ $P = \frac{1}{3}\rho \bar{c^2}$ কণার স্থিতিস্থাপক সংঘর্ষ ও ভরবেগ পরিবর্তনের ভিত্তিতে ধাপে ধাপে প্রতিপাদন করো। প্রতিপাদনে 'আইসোট্রপিক গতির' তাৎপর্য ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>চাপ সমীকরণের আণবিক গতিবিদ্যাভিত্তিক নিখুঁত প্রতিপাদন:</t>
@@ -1718,11 +1663,6 @@
           <t>গ্যাসের চাপ $P$ এবং একক আয়তনের গতিশক্তি ঘনত্ব $E_V$-এর মধ্যে সম্পর্ক $P = \frac{2}{3}E_V$ প্রতিপাদন করো। প্রমাণ করো যে $1\text{ mol}$ আদর্শ গ্যাসের মোট স্থানান্তর গতিশক্তি $E_k = \frac{3}{2}R T$ এবং একটি একক অণুর গড় গতিশক্তি $\bar{\varepsilon} = \frac{3}{2}k_B T$, যা কেবল তাপমাত্রার ওপর নির্ভর করে, গ্যাসের ধরনের ওপর নয়।</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>চাপ ও গতিশক্তির সম্পর্ক এবং তাপমাত্রার গতিতাত্ত্বিক ব্যাখ্যা:</t>
@@ -1768,11 +1708,6 @@
           <t>আণবিক গতির তিনটি প্রধান দ্রুতি: (i) মূল-গড়-বর্গ দ্রুতি $c_{\text{rms}} = \sqrt{\frac{3RT}{M}}$, (ii) গড় দ্রুতি $\bar{c} = \sqrt{\frac{8RT}{\pi M}}$, এবং (iii) সর্বাধিক সম্ভাব্য দ্রুতি $c_p = \sqrt{\frac{2RT}{M}}$। এদের অনুপাত $c_p : \bar{c} : c_{\text{rms}}$ নির্ণয় করো। $0^\circ\text{C}$ তাপমাত্রায় হাইড্রোজেন গ্যাসের অণুর $c_{\text{rms}}$ এবং অক্সিজেনের $c_{\text{rms}}$ কত? [$R = 8.314\text{ J mol}^{-1}\text{ K}^{-1}$]</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>তিন প্রকার আণবিক দ্রুতির অনুপাত ও সাংখ্যিক মান:</t>
@@ -1818,11 +1753,6 @@
           <t>চাঁদে কোনো বায়ুমণ্ডল নেই কেন? চাঁদের পৃষ্ঠে মুক্তিবেগ $v_e = 2.38\text{ km s}^{-1}$ এবং চান্দ্র দিবসে চাঁদের পৃষ্ঠের তাপমাত্রা প্রায় $100^\circ\text{C}$ ($373\text{ K}$)। হাইড্রোজেন ও নাইট্রোজেন গ্যাসের অণুর RMS গতিবেগের সাথে চাঁদের মুক্তিবেগের তুলনা করে বায়ুমণ্ডলের অনুপস্থিতির কারণ ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>চাঁদে মুক্তিবেগ বনাম তাপীয় গতির পালানোর শর্ত বিশ্লেষণ:</t>
@@ -1868,11 +1798,6 @@
           <t>একটি পাত্রে হিলিয়াম ($\text{He}$) এবং আর্গন ($\text{Ar}$) গ্যাসের একটি সম-ভর মিশ্রণ রয়েছে। গ্যাস মিশ্রণটির তাপমাত্রা $T$। (i) হিলিয়াম এবং আর্গন অণুর গড় স্থানান্তর গতিশক্তির অনুপাত কত? (ii) তাদের আরএমএস দ্রুতির অনুপাত কত? [হিলিয়ামের পারমাণবিক ভর $4$ এবং আর্গনের $40$]</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>গ্যাস মিশ্রণে গতিশক্তি বনাম আরএমএস দ্রুতির অনুপাত তুলনা:</t>
@@ -1918,11 +1843,6 @@
           <t>একটি পাত্রে আবদ্ধ কোনো গ্যাসের পরম তাপমাত্রা $4$ গুণ বৃদ্ধি করা হলে এবং পাত্রের আয়তন অর্ধেক ($V/2$) করা হলে গ্যাসের অণুগুলির আরএমএস দ্রুতি এবং পাত্রের দেয়ালে প্রযুক্ত চাপ কত গুণ বৃদ্ধি পাবে?</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>তাপমাত্রা ও আয়তন পরিবর্তনে আরএমএস দ্রুতি ও চাপের স্কেলিং:</t>
@@ -1968,11 +1888,6 @@
           <t>একটি সমতল দেয়ালের দিকে একটি আদর্শ গ্যাসের অণুসমূহ আপতিত হচ্ছে। দেয়ালটি যদি অণুগুলির আপতনের অভিমুখে সমবেগ $u$ নিয়ে এগিয়ে যায়, তবে একটি অণুর দেয়ালের সাথে স্থিতিস্থাপক সংঘর্ষের পর তার বেগের পরিবর্তন কত হবে? এটি কীভাবে গ্যাসের রুদ্ধতাপীয় সংকোচনে তাপমাত্রা বৃদ্ধির ব্যাখ্যা দেয়?</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>গতিশীল দেয়ালে সংঘর্ষ এবং রুদ্ধতাপীয় উষ্ণায়ন:</t>
@@ -2018,11 +1933,6 @@
           <t>একটি আবদ্ধ ঘরের বাতাসের তাপমাত্রা $15^\circ\text{C}$ থেকে হিটার চালিয়ে $25^\circ\text{C}$-এ উন্নীত করা হলো। যদি বায়ুমণ্ডলীয় চাপ অপরিবর্তিত থাকে এবং ঘরটি নিখুঁতভাবে বায়ু নিরোধক না হয় (বাতাস বের হতে পারে), তবে ঘরের ভেতরে বিদ্যমান বাতাসের মোট অভ্যন্তরীণ শক্তি হ্রাস পাবে, বৃদ্ধি পাবে, নাকি অপরিবর্তিত থাকবে?</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>স্থির চাপে খোলা ঘরে অভ্যন্তরীণ শক্তির নিত্যতার কৌতূহলোদ্দীপক ফলাফল:</t>
@@ -2068,11 +1978,6 @@
           <t>নির্দিষ্ট ভরের একটি আদর্শ গ্যাসের অণুসমূহের মূল-গড়-বর্গ দ্রুতি $c_{\text{rms}}$ এবং পরম শূন্য তাপমাত্রার তাৎপর্য ব্যাখ্যা করো। গ্যাসের চাপ বা আয়তন শূন্য হওয়ার আগেই কেন গ্যাস তরল বা কঠিনে রূপান্তরিত হয় এবং কেন গতিতত্ত্বের আদর্শ আচরণ পরম শূন্যের নিকটে ভেঙে পড়ে?</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>পরম শূন্য তাপমাত্রা ও গতিতত্ত্বের সীমার কারণ:</t>
@@ -2118,11 +2023,6 @@
           <t>$1\text{ L}$ আয়তনের একটি ফ্লাস্কে $10^{-6}\text{ mm-Hg}$ উচ্চ শূন্যতায় (ultra-high vacuum) এবং $300\text{ K}$ তাপমাত্রায় কতটি অবশিষ্ট গ্যাসের অণু বিদ্যমান থাকবে? [$1\text{ atm} = 760\text{ mm-Hg} = 1.013 \times 10^5\text{ Pa}$, $k_B = 1.38 \times 10^{-23}\text{ J K}^{-1}$]</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>উচ্চ শূন্যতায় অবশিষ্ট অণু সংখ্যার গণনা:</t>
@@ -2219,11 +2119,6 @@
           <t>ম্যাক্সওয়েল বন্টন অপেক্ষক ব্যবহার করে সমাকলনের মাধ্যমে অণুর গড় দ্রুতি $\bar{v} = \int_0^\infty v f(v) dv = \sqrt{\frac{8 k_B T}{\pi m}}$ প্রতিপাদন করো। [প্রয়োজনীয় প্রমাণ সমাকলন: $\int_0^\infty x^3 e^{-\alpha x^2} dx = \frac{1}{2\alpha^2}$]</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>গামা সমাকলনের সাহায্যে গড় দ্রুতির প্রতিপাদন:</t>
@@ -2269,11 +2164,6 @@
           <t>ম্যাক্সওয়েল বন্টন ব্যবহার করে প্রমাণ করো যে অণুর মূল-গড়-বর্গ দ্রুতি $v_{\text{rms}} = \sqrt{\int_0^\infty v^2 f(v) dv} = \sqrt{\frac{3 k_B T}{m}}$। [প্রয়োজনীয় সমাকলন: $\int_0^\infty x^4 e^{-\alpha x^2} dx = \frac{3\sqrt{\pi}}{8\alpha^{5/2}}$]</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>ম্যাক্সওয়েল বন্টন থেকে আরএমএস দ্রুতির প্রতিপাদন:</t>
@@ -2319,11 +2209,6 @@
           <t>দ্বিমাত্রিক তলে (2D gas, যেমন গ্রাফিনের ওপর শোষিত গ্যাস অণু) ম্যাক্সওয়েল-বোল্টজম্যান দ্রুতি বন্টন অপেক্ষক $f(v_{2D}) = \left(\frac{m}{k_B T}\right) v e^{-\frac{m v^2}{2 k_B T}}$ প্রতিপাদন করো। দ্বিমাত্রিক গ্যাসে সর্বাধিক সম্ভাব্য দ্রুতি $v_p$ এবং গড় দ্রুতি $\bar{v}$-এর মান কত?</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>দ্বিমাত্রিক ম্যাক্সওয়েল দ্রুতি বন্টন ও চরম মান বিশ্লেষণ:</t>
@@ -2369,11 +2254,6 @@
           <t>একটি পাত্রের সূক্ষ্ম ছিদ্র দিয়ে গ্যাসহীন বায়ুশূন্য স্থানে অণুসমূহের নিঃসরণ (effusion) প্রক্রিয়া বিশ্লেষণ করো। দেখাও যে নিঃসৃত অণুগুলির গড় গতিশক্তি পাত্রের ভেতরে থাকা অণুগুলির গড় গতিশক্তির তুলনায় বেশি হয় এবং নিঃসৃত অণুগুলির গড় শক্তি $\bar{E}_{\text{eff}} = 2 k_B T$ (পাত্রের ভেতরে যেখানে $\frac{3}{2} k_B T$)।</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>ছিদ্রপথে নিঃসৃত অণুর গতিশক্তি বৃদ্ধি প্রমাণ:</t>
@@ -2419,11 +2299,6 @@
           <t>অণুসমূহের গতিশক্তি $E = \frac{1}{2}m v^2$-এর নিরিখে ম্যাক্সওয়েল শক্তি বন্টন সূত্র $f(E)dE = \frac{2}{\sqrt{\pi}}(k_B T)^{-3/2} E^{1/2} e^{-\frac{E}{k_B T}} dE$ প্রতিপাদন করো। দেখাও যে সর্বাধিক সম্ভাব্য গতিশক্তি $E_p = \frac{1}{2}k_B T$, অথচ সর্বাধিক সম্ভাব্য দ্রুতির গতিশক্তি $\frac{1}{2}m v_p^2 = k_B T$। এই পার্থক্যের কারণ কী?</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>গতিশক্তি বন্টন প্রতিপাদন ও $E_p$ বনাম $\frac{1}{2}mv_p^2$-এর পার্থক্যের কারণ:</t>
@@ -2469,11 +2344,6 @@
           <t>গ্যাসে তাপীয় গতির কারণে নির্গত বর্ণালী রেখার ডপলার সম্প্রসারণ (Doppler broadening of spectral lines) ঘটে। গ্যাস অণুগুলির গতির কারণে একটি বর্ণালী রেখার পূর্ণ বিস্তার অর্ধ-উচ্চতা (FWHM $\Delta \lambda_D$) কীভাবে $\Delta \lambda_D = \lambda_0 \sqrt{\frac{8 k_B T \ln 2}{M c^2}}$ রূপ ধারণ করে তা ম্যাক্সওয়েলিয়ান বেগ বন্টন থেকে ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>বর্ণালী রেখার তাপীয় ডপলার সম্প্রসারণ প্রতিপাদন:</t>
@@ -2519,11 +2389,6 @@
           <t>ম্যাক্সওয়েল দ্রুতি বন্টনের উচ্চ গতির লেজ (high-speed tail) রাসায়নিক বিক্রিয়ার সক্রিয়করণ শক্তি (activation energy $E_a$) এবং আরহেনিয়াস সমীকরণ $k = A e^{-E_a / R T}$-এর সাথে কীভাবে সম্পর্কিত? তাপমাত্রা সামান্য বৃদ্ধি করলে বিক্রিয়ার হার বহুগুণ বেড়ে যাওয়ার ব্যাখ্যা গতিতত্ত্বের সাহায্যে দাও।</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>আরহেনিয়াস সমীকরণ ও ম্যাক্সওয়েল টেল বিশ্লেষণের সম্পর্ক:</t>
@@ -2569,11 +2434,6 @@
           <t>জার্টম্যান ও কো-এর পরীক্ষা (Zartman and Ko experiment) কীভাবে একটি ঘূর্ণায়মান চোঙ (rotating cylinder) ব্যবহার করে গ্যাসের অণুর ম্যাক্সওয়েল দ্রুতি বন্টন সরাসরি পরীক্ষামূলকভাবে প্রমাণ করেছিল?</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>জার্টম্যান-কো ঘূর্ণন সিলিন্ডার পরীক্ষার কৌশল:</t>
@@ -2619,11 +2479,6 @@
           <t>একটি গ্যাসে কোনো নির্দিষ্ট মুহূর্তে কত ভগ্নাংশ অণুর দ্রুতি সর্বাধিক সম্ভাব্য দ্রুতি $v_p$ এবং $1.01 v_p$-এর সংকীর্ণ সীমার মধ্যে অবস্থান করবে? ফলাফলটি তাপমাত্রার ওপর নির্ভর করে কি না যাচাই করো।</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>সংকীর্ণ দ্রুতি ব্যবধানে অণুর ভগ্নাংশ গণনা ও তাপমাত্রা নিরপেক্ষতা:</t>
@@ -2669,11 +2524,6 @@
           <t>স্বাতন্ত্র্য মাত্রা (Degrees of Freedom, $f$) বলতে কী বোঝায়? বোল্টজম্যানের শক্তির সমবিভাজন নীতিটি বিবৃত করো এবং দেখাও যে $f$ স্বাতন্ত্র্য মাত্রার অণুর জন্য $1\text{ mol}$ গ্যাসের অভ্যন্তরীণ শক্তি $U = \frac{f}{2}R T$, স্থির আয়তনে মোলার তাপধারণ ক্ষমতা $C_v = \frac{f}{2}R$, স্থির চাপে মোলার তাপধারণ ক্ষমতা $C_p = \left(\frac{f}{2} + 1\right)R$ এবং এদের অনুপাত $\gamma = 1 + \frac{2}{f}$।</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>স্বাতন্ত্র্য মাত্রা থেকে তাপধারণ ক্ষমতা ও গামা প্রতিপাদন:</t>
@@ -2719,11 +2569,6 @@
           <t>এক-পরমাণুক ($\text{He}$), দ্বি-পরমাণুক ($\text{O}_2$) এবং ত্রি-পরমাণুক অসরলরৈখিক ($\text{H}_2\text{O}$) গ্যাসের জন্য কক্ষ তাপমাত্রায় স্বাতন্ত্র্য মাত্রা $f$, $C_v$, $C_p$ এবং $\gamma$-এর তাত্ত্বিক মান ছক আকারে নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>বিভিন্ন পারমাণবিকতার গ্যাসের তাত্ত্বিক গামা বিশ্লেষণ:</t>
@@ -2769,11 +2614,6 @@
           <t>কোয়ান্টাম বরফায়ন (Quantum freeze-out of degrees of freedom) কী? হাইড্রোজেন গ্যাসের ($H_2$) ক্ষেত্রে অতি নিম্ন তাপমাত্রায় ($T &lt; 50\text{ K}$) $\gamma = 1.67$, কক্ষ তাপমাত্রায় ($300\text{ K}$) $\gamma = 1.40$, এবং অতি উচ্চ তাপমাত্রায় ($T &gt; 1000\text{ K}$) $\gamma = 1.29$ হয় কেন? ক্লাসিক্যাল পদার্থবিজ্ঞান কেন এই ঘটনা ব্যাখ্যায় ব্যর্থ হয়েছিল?</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>হাইড্রোজেনের আপেক্ষিক তাপের কোয়ান্টাম ধাপীয় রূপান্তর:</t>
@@ -2819,11 +2659,6 @@
           <t>কঠিন পদার্থের ক্ষেত্রে ডুলং ও পেটিটের সূত্র (Dulong-Petit Law) $C_m = 3R \approx 24.9\text{ J mol}^{-1}\text{ K}^{-1}$ শক্তির সমবিভাজন নীতির সাহায্যে প্রতিপাদন করো। কঠিনের প্রতিটি পরমাণুর স্বাতন্ত্র্য মাত্রা কেন $6$ ধরা হয়?</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>ডুলং-পেটিটের সূত্র ও ত্রিমাত্রিক সরল ছন্দিত স্পন্দকের সমবিভাজন:</t>
@@ -2869,11 +2704,6 @@
           <t>একটি গ্যাস মিশ্রণে $2\text{ mol}$ হিলিয়াম ($\gamma_1 = 5/3$) এবং $3\text{ mol}$ অক্সিজেন ($\gamma_2 = 7/5$) মিশ্রিত আছে। মিশ্রণটির জন্য সমতুল্য মোলার তাপধারণ ক্ষমতা $C_{v,\text{mix}}$, $C_{p,\text{mix}}$ এবং কার্যকর $\gamma_{\text{mix}}$ নির্ণয় করো। মিশ্রণটির এক মোলের তাপমাত্রা $1\text{ K}$ বাড়াতে কত তাপ প্রয়োজন?</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>গ্যাস মিশ্রণে কার্যকর তাপধারণ ক্ষমতা ও গামা গণনা:</t>
@@ -2919,11 +2749,6 @@
           <t>একটি অনমনীয় রৈখিক ত্রি-পরমাণুক অণু যেমন কার্বন ডাই অক্সাইড ($\text{O}=\text{C}=\text{O}$)-এর কম্পন ব্যতীত মোট স্বাতন্ত্র্য মাত্রা কত? যদি কক্ষ তাপমাত্রায় দুটি ব্যন্ডিং মোড (bending modes) এবং দুটি স্ট্রেচিং মোড (stretching modes) সক্রিয় থাকে, তবে অণুটির সর্বোচ্চ স্বাতন্ত্র্য মাত্রা এবং $\gamma$-এর তাত্ত্বিক মান কত হবে?</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>রৈখিক পলিঅ্যাটমিক অণুর কম্পন মোড ও স্বাতন্ত্র্য মাত্রা বিশ্লেষণ:</t>
@@ -2969,11 +2794,6 @@
           <t>একটি দ্বি-পরমাণুক গ্যাসের $1\text{ mol}$ পরিমাণকে স্থির চাপে $Q = 70\text{ J}$ তাপ প্রদান করা হলো। গ্যাসটির অভ্যন্তরীণ শক্তি কত বৃদ্ধি পাবে এবং গ্যাস কর্তৃক সম্পাদিত কাজের মান কত? প্রদত্ত তাপের কত ভগ্নাংশ বাহ্যিক কাজে রূপান্তরিত হয়?</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>স্থির চাপে প্রথম তাপগতি সূত্র ও কাজের ভগ্নাংশ নির্ণয়:</t>
@@ -3019,11 +2839,6 @@
           <t>একটি অনমনীয় বাক্সে $T = 300\text{ K}$ তাপমাত্রায় $n = 1\text{ mol}$ এক-পরমাণুক আদর্শ গ্যাস আবদ্ধ আছে। বাক্সটিকে একটি ট্রেনের কামরায় রাখা হলো যা $v = 100\text{ m s}^{-1}$ অনুভূমিক দ্রুতিতে চলছে। ট্রেনটি হঠাৎ ব্রেক কষে থামলে ট্রেনের গতিশক্তি সম্পূর্ণরূপে গ্যাসে শোষিত হয়। গ্যাসের তাপমাত্রা কত বৃদ্ধি পাবে? [গ্যাসের মোলার ভর $M = 0.040\text{ kg mol}^{-1}$, $R = 8.314\text{ J mol}^{-1}\text{ K}^{-1}$]</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>সামগ্রিক গতিশক্তি তাপীয় অভ্যন্তরীণ শক্তিতে রূপান্তর:</t>
@@ -3069,11 +2884,6 @@
           <t>শক্তির সমবিভাজন নীতি কি মহাকর্ষীয় বিভব শক্তি বা অতি উচ্চ গতিবেগে (আপেক্ষিকীয় গতি) প্রযোজ্য? চরম আপেক্ষিকীয় গ্যাসে (ultra-relativistic gas, $E = p c$) সমবিভাজন নীতি অনুসারে প্রতি স্বাতন্ত্র্য মাত্রায় গড় শক্তি $\frac{1}{2}k_B T$-এর বদলে $k_B T$ হয় কেন?</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>আপেক্ষিকীয় গ্যাস ও সমবিভাজন নীতির সাধারণ রূপ:</t>
@@ -3170,11 +2980,6 @@
           <t>গ্যাসের অণুর গড় মুক্ত পথ (mean free path $\lambda$) বলতে কী বোঝায়? ক্লসিয়াসের প্রাথমিক সূত্র $\lambda_C = \frac{1}{\pi n d^2}$ এবং ম্যাক্সওয়েলের আপেক্ষিক গতির সংশোধন দ্বারা $\lambda = \frac{1}{\sqrt{2}\pi n d^2}$ প্রতিপাদন করো, যেখানে $n$ হলো সংখ্যা ঘনত্ব এবং $d$ অণুর আণবিক ব্যাস। ম্যাক্সওয়েলের সূত্রে $\sqrt{2}$ ফ্যাক্টরটি কেন আসে?</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>গড় মুক্ত পথের ক্লসিয়াস ও ম্যাক্সওয়েল সূত্রের প্রতিপাদন:</t>
@@ -3220,11 +3025,6 @@
           <t>গড় মুক্ত পথের সমীকরণকে তাপমাত্রা $T$ এবং চাপ $P$-এর মাধ্যমে $\lambda = \frac{k_B T}{\sqrt{2}\pi d^2 P}$ আকারে প্রকাশ করো। প্রমাণ করো যে: (i) স্থির তাপমাত্রায় চাপ দ্বিগুণ করলে গড় মুক্ত পথ অর্ধেক হয়ে যায়, এবং (ii) স্থির আয়তনে একটি আবদ্ধ পাত্রে গ্যাসের তাপমাত্রা বৃদ্ধি করলে গড় মুক্ত পথ সম্পূর্ণ অপরিবর্তিত থাকে।</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>গড় মুক্ত পথের চাপ ও তাপমাত্রা নির্ভরতা বিশ্লেষণ:</t>
@@ -3270,11 +3070,6 @@
           <t>প্রমাণ তাপমাত্রা ও চাপে ($P = 1.013 \times 10^5\text{ Pa}$, $T = 273\text{ K}$) নাইট্রোজেন গ্যাসের অণুর গড় মুক্ত পথ নির্ণয় করো। অণুর কার্যকর ব্যাস $d = 0.3\text{ nm}$ এবং গড় দ্রুতি $\bar{v} = 450\text{ m s}^{-1}$। প্রতি সেকেন্ডে একটি অণু গড়ে কতবার সংঘর্ষে লিপ্ত হয় (সংঘর্ষ কম্পাঙ্ক $Z$)? [$k_B = 1.38 \times 10^{-23}\text{ J K}^{-1}$]</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>এসটিপিতে নাইট্রোজেনের গড় মুক্ত পথ ও সংঘর্ষ কম্পাঙ্ক গণনা:</t>
@@ -3320,11 +3115,6 @@
           <t>গ্যাসের সান্দ্রতা গুণাঙ্ক (coefficient of viscosity) $\eta = \frac{1}{3}\rho \bar{v}\lambda$ প্রতিপাদন করো। ম্যাক্সওয়েলের বিখ্যাত ভবিষ্যদ্বাণী ব্যাখ্যা করো: বিস্তৃত চাপের পাল্লায় একটি গ্যাসের সান্দ্রতা চাপের ওপর মোটেও নির্ভর করে না ($\eta \propto P^0$)। তাপমাত্রা বৃদ্ধি পেলে তরলের সান্দ্রতা হ্রাস পেলেও গ্যাসের সান্দ্রতা বৃদ্ধি পায় কেন?</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>গ্যাসের সান্দ্রতার চাপ নিরপেক্ষতা ও তাপমাত্রা নির্ভরতা প্রতিপাদন:</t>
@@ -3370,11 +3160,6 @@
           <t>গ্যাসের তাপ পরিবাহিতাঙ্ক $K = \frac{1}{3}\rho \bar{v}\lambda C_v$ প্রতিপাদন করো। সান্দ্রতার মতো তাপ পরিবাহিতাও কেন সাধারণ চাপে চাপের ওপর নির্ভর করে না? ডিউয়ার ফ্লাস্কের (Dewar/Thermos flask) দুই দেয়ালের মধ্যবর্তী স্থান কেন অতি উচ্চ ভ্যাকুয়ামে রাখা হয়?</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>গ্যাসের তাপ পরিবাহিতা ও থার্মাস ফ্লাস্কের ভ্যাকুয়াম মেকানিজম:</t>
@@ -3420,11 +3205,6 @@
           <t>গ্যাসে স্ব-ব্যাপন গুণাঙ্ক (self-diffusion coefficient) $D = \frac{1}{3}\bar{v}\lambda$ প্রতিপাদন করো। দেখাও যে ব্যাপন গুণাঙ্ক তাপমাত্রার সাথে $D \propto \frac{T^{3/2}}{P}$ অনুসারে পরিবর্তিত হয়। গন্ধযুক্ত কোনো গ্যাসের বোতল ঘরের এক কোণে খুললে তা অপর কোণে পৌঁছাতে কয়েক মিনিট সময় লাগে কেন, যেখানে অণুগুলোর গতিবেগ সেকেন্ডে প্রায় $500\text{ m}$?</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>ব্যাপন গুণাঙ্কের তাপমাত্রা-চাপ নির্ভরতা ও গন্ধ ছড়ানোর বিলম্বের ব্যাখ্যা:</t>
@@ -3470,11 +3250,6 @@
           <t>নুডসেন সংখ্যা (Knudsen number $Kn = \frac{\lambda}{L}$) কী? $Kn \ll 1$ এবং $Kn \gg 1$ সীমার মধ্যে তরল বলবিদ্যার আচরণের পার্থক্য কী? মহাকাশযানের বায়ুমণ্ডলে পুনঃপ্রবেশের (re-entry) সময় নুডসেন সংখ্যার তাৎপর্য ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>নুডসেন সংখ্যা ও অবিচ্ছিন্ন বনাম মুক্ত আণবিক প্রবাহ:</t>
@@ -3520,11 +3295,6 @@
           <t>তাপীয় নিঃস্বেদন বা থার্মাল ট্রান্সপিরেশন (Thermal Transpiration / Reynolds' effect) কী? একটি ক্ষুদ্র সূক্ষ্ম ছিদ্রযুক্ত দেয়াল দ্বারা দুটি পাত্র যুক্ত আছে যাদের তাপমাত্রা যথাক্রমে $T_1$ এবং $T_2$। যদি ছিদ্রের ব্যাস গড় মুক্ত পথের তুলনায় অত্যন্ত ক্ষুদ্র হয় ($d \ll \lambda$), তবে সাম্যাবস্থায় উভয় পাত্রের চাপের অনুপাত $\frac{P_1}{P_2} = \sqrt{\frac{T_1}{T_2}}$ প্রতিপাদন করো।</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>থার্মাল ট্রান্সপিরেশন ও রেনল্ডসের অ-সমান চাপ সাম্যাবস্থা:</t>
@@ -3570,11 +3340,6 @@
           <t>ক্রুকসের রেডিওমিটারের (Crookes radiometer) ফাঁপা কাঁচের বাল্বে থাকা হালকা পাখাগুলোর এক পাশ কালো এবং অপর পাশ রূপালী চকচকে। আলো ফেললে পাখাগুলো কালো পৃষ্ঠের দিকে ধাক্কা খেয়ে ঘোরে। এই ঘূর্ণনের সঠিক কারণ কী? বাল্বটিতে নিখুঁত অতি-উচ্চ ভ্যাকুয়াম সৃষ্টি করলে পাখাগুলোর ঘূর্ণন বন্ধ হয়ে যায় কেন?</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>ক্রুকসের রেডিওমিটারের তাপীয় ট্রানজিশনাল মেকানিজম:</t>
@@ -3620,11 +3385,6 @@
           <t>একটি অণুর আণবিক ব্যাস $d = 2\text{ Å} = 0.2\text{ nm}$। গ্যাসের তাপমাত্রা $T = 300\text{ K}$। চাপ কত নিচে নামালে অণুটির গড় মুক্ত পথ $\lambda = 1.0\text{ m}$ হবে? পরীক্ষাগারে কণা ত্বরক যন্ত্রে (particle accelerator) কেন এই মাত্রার অতি-উচ্চ ভ্যাকুয়াম বজায় রাখা অপরিহার্য?</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>১ মিটার গড় মুক্ত পথের জন্য প্রয়োজনীয় ভ্যাকুয়াম চাপ গণনা:</t>
@@ -3654,7 +3414,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>হ্রদের গভীরতা ও বুদবুদ প্রসারণ (সমস্যা 1)</t>
+          <t>গ্যাস সূত্র ও হ্রদের বুদবুদ প্রসারণ (Gas Laws &amp; Lake Bubble Expansion)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3663,34 +3423,29 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>[সমস্যা 1: হ্রদের গভীরতা ও বুদবুদ প্রসারণ]
-##PRESET:pv-diagram(isothermal)[size:medium]##
-একটি হ্রদের তলদেশ হতে একটি বায়ুর বুদবুদ পানির উপরিপৃষ্ঠে উঠে আসায় এর আয়তন 3 গুণ হয়। বায়ুমণ্ডলীয় চাপ $1.013 \times 10^5\text{ Pa}$, পানির ঘনত্ব $1000\text{ kg/m}^3$, এবং তাপমাত্রা ধ্রুব থাকলে হ্রদের গভীরতা কত? ($g = 9.8\text{ m/s}^2$)</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি হ্রদের তলদেশ থেকে একটি বায়ুর বুদবুদ উপরিপৃষ্ঠে উঠে আসায় এর আয়তন $4$ গুণ হয়ে যায়। বায়ুমণ্ডলীয় চাপ $10^5\text{ Pa}$, পানির ঘনত্ব $1000\text{ kg/m}^3$ এবং তলদেশ ও পৃষ্ঠের তাপমাত্রা যথাক্রমে $7^\circ\text{C}$ ও $27^\circ\text{C}$ হলে হ্রদের গভীরতা $h$ কত? ($g = 9.8\text{ ms}^{-2}$)।</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>##PRESET:pv-diagram(isothermal)[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 1)।</t>
+          <t>তলদেশে চাপ $P_1 = P_0 + h\rho g$, আয়তন $V_1$, তাপমাত্রা $T_1 = 273 + 7 = 280\text{ K}$। পৃষ্ঠে চাপ $P_2 = P_0 = 10^5\text{ Pa}$, আয়তন $V_2 = 4V_1$, তাপমাত্রা $T_2 = 273 + 27 = 300\text{ K}$। আদর্শ গ্যাস সমীকরণ: $\frac{P_1 V_1}{T_1} = \frac{P_2 V_2}{T_2} \implies \frac{(P_0 + h\rho g)V_1}{280} = \frac{P_0 (4V_1)}{300} \implies P_0 + h\rho g = P_0 \left(\frac{4 \times 280}{300}\right) = P_0 \left(\frac{1120}{300}\right) = 3.7333 P_0$। অতএব $h\rho g = 2.7333 P_0 = 2.7333 \times 10^5 \implies h = \frac{2.7333 \times 10^5}{1000 \times 9.8} = \frac{273333}{9800} \approx 27.89\text{ m}$।</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>হ্রদের গভীরতা $h = 27.89\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3710,12 +3465,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>গ্যাসের অণুর আরএমএস বেগ (সমস্যা 2)</t>
+          <t>গ্যাস সূত্র ও হ্রদের বুদবুদ প্রসারণ (Gas Laws &amp; Lake Bubble Expansion)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -3723,30 +3478,25 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>[সমস্যা 2: গ্যাসের অণুর আরএমএস বেগ]
-##PRESET:maxwell-distribution[size:medium]##
-$47^\circ\text{C}$ তাপমাত্রায় নাইট্রোজেন ($N_2$) গ্যাসের অণুর মূল গড় বর্গবেগ ($c_{rms} = \sqrt{\frac{3RT}{M}}$) কত নির্ণয় কর। ($R = 8.314\text{ J/(mol}\cdot\text{K)}, M = 28 \times 10^{-3}\text{ kg/mol}$)</t>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##
+স্বাভাবিক তাপমাত্রা ও চাপে ($0^\circ\text{C}, 1.013 \times 10^5\text{ Pa}$) $32\text{ g}$ অক্সিজেন গ্যাসের আয়তন $22.4\text{ L}$। যদি চাপ দ্বিগুণ এবং তাপমাত্রা $100^\circ\text{C}$ করা হয়, তবে ওই গ্যাসের নতুন আয়তন কত লিটার হবে?</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>##PRESET:maxwell-distribution[size:medium]##</t>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 2)।</t>
+          <t>$\frac{P_1 V_1}{T_1} = \frac{P_2 V_2}{T_2} \implies V_2 = V_1 \left(\frac{P_1}{P_2}\right)\left(\frac{T_2}{T_1}\right)$। মান বসিয়ে: $V_2 = 22.4 \times \left(\frac{1}{2}\right) \times \left(\frac{373.15}{273.15}\right) = 11.2 \times 1.3661 \approx 15.30\text{ L}$।</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 2</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>নতুন আয়তন $V_2 = 15.30\text{ L}$</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3766,7 +3516,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>আপেক্ষিক আর্দ্রতা ও শিশিরাংক (সমস্যা 3)</t>
+          <t>গ্যাস সূত্র ও হ্রদের বুদবুদ প্রসারণ (Gas Laws &amp; Lake Bubble Expansion)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3775,29 +3525,29 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>[সমস্যা 3: আপেক্ষিক আর্দ্রতা ও শিশিরাংক]
-কোনো একদিন বায়ুর তাপমাত্রা $50^\circ\text{C}$ এবং শিশিরাংক $9^\circ\text{C}$। $9^\circ\text{C}$ ও $50^\circ\text{C}$-এ সম্পৃক্ত জলীয় বাষ্পের চাপ যথাক্রমে $9.2\text{ mm-Hg}$ এবং $17.5\text{ mm-Hg}$ হলে ঐ দিনের আপেক্ষিক আর্দ্রতা কত?</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##
+একটি আবদ্ধ সিলিন্ডারে $27^\circ\text{C}$ তাপমাত্রায় এবং $3.0\text{ atm}$ চাপে কিছু গ্যাস রয়েছে। সিলিন্ডারের নিরাপত্তা ভালভ সর্বোচ্চ $5.0\text{ atm}$ চাপ সহ্য করতে পারে। কত তাপমাত্রায় উত্তপ্ত করলে সিলিন্ডারটি ফেটে যাওয়ার উপক্রম হবে?</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 3)।</t>
+          <t>আয়তন স্থির থাকায় গে-লুসাকের সূত্র: $\frac{P_1}{T_1} = \frac{P_2}{T_2} \implies T_2 = T_1\frac{P_2}{P_1} = (273 + 27)\frac{5.0}{3.0} = 300 \times \frac{5}{3} = 500.0\text{ K}$। সেলসিয়াসে $\theta_2 = 500 - 273 = 227.0^\circ\text{C}$।</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 3</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>তাপমাত্রা $T_2 = 500.0\text{ K} = 227.0^\circ\text{C}$</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3817,12 +3567,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>গ্যাসের মোট গতিশক্তি ও চাপ (সমস্যা 4)</t>
+          <t>গ্যাস সূত্র ও হ্রদের বুদবুদ প্রসারণ (Gas Laws &amp; Lake Bubble Expansion)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -3830,25 +3580,25 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>[সমস্যা 4: গ্যাসের মোট গতিশক্তি ও চাপ]
-একটি $V = 6\text{ m}^3$ আয়তনের পাত্রে $P = 11 \times 10^5\text{ Pa}$ চাপে গ্যাস আবদ্ধ আছে। পাত্রে রক্ষিত সমগ্র গ্যাসের মোট গতিশক্তি ($E_k = \frac{3}{2}PV$) কত জুল?</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+একটি কাচ পাত্রে $27^\circ\text{C}$ তাপমাত্রায় বাতাস পূর্ণ আছে। পাত্রটিকে কত তাপমাত্রায় উত্তপ্ত করলে প্রারম্ভিক বাতাসের এক-তৃতীয়াংশ ($1/3$ অংশ) বাতাস বের হয়ে যাবে? (চাপ অপরিবর্তিত)।</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 4)।</t>
+          <t>চাপ স্থির থাকলে $n_1 T_1 = n_2 T_2$। প্রারম্ভিক মোল $n_1$, বের হয়ে যাওয়ার পর অবশিষ্ট মোল $n_2 = n_1 - \frac{1}{3}n_1 = \frac{2}{3}n_1$। অতএব $n_1(300) = \left(\frac{2}{3}n_1\right)T_2 \implies T_2 = \frac{300 \times 3}{2} = 450.0\text{ K}$। সেলসিয়াসে $\theta_2 = 450 - 273 = 177.0^\circ\text{C}$।</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 4</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>তাপমাত্রা $T_2 = 450.0\text{ K} = 177.0^\circ\text{C}$</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3868,7 +3618,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>স্বাধীনতার মাত্রা ও মোলার তাপধারণ ক্ষমতা (সমস্যা 5)</t>
+          <t>গ্যাস সূত্র ও হ্রদের বুদবুদ প্রসারণ (Gas Laws &amp; Lake Bubble Expansion)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3877,29 +3627,29 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>[সমস্যা 5: স্বাধীনতার মাত্রা ও মোলার তাপধারণ ক্ষমতা]
-একটি দ্বি-পরমাণুক আদর্শ গ্যাসের স্বাধীনতার মাত্রা $f = 5$ হলে গ্যাসটির স্থির চাপে ও স্থির আয়তনে মোলার আপেক্ষিক তাপদ্বয়ের অনুপাত $\gamma = C_p / C_v$ কত?</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2.5,h=4][size:small]##
+একটি $10.0\text{ L}$ আয়তনের ফ্লাস্কে $27^\circ\text{C}$ তাপমাত্রায় $4.0\text{ g}$ হিলিয়াম ($M = 4$) এবং $16.0\text{ g}$ অক্সিজেন ($M = 32$) গ্যাসের মিশ্রণ রয়েছে। মিশ্রণের মোট চাপ $P$ এবং গ্যাসদ্বয়ের আংশিক চাপ ডাল্টনের সূত্রানুযায়ী নির্ণয় কর। ($R = 8.314\text{ J/mol}\cdot\text{K}$)।</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2.5,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 5)।</t>
+          <t>হিলিয়ামের মোল $n_1 = \frac{4}{4} = 1.0\text{ mol}$, অক্সিজেনের মোল $n_2 = \frac{16}{32} = 0.5\text{ mol}$। মোট মোল $n = 1.5\text{ mol}$। আয়তন $V = 10 \times 10^{-3}\text{ m}^3$, $T = 300\text{ K}$। মোট চাপ $P = \frac{n R T}{V} = \frac{1.5 \times 8.314 \times 300}{0.010} = \frac{3741.3}{0.010} = 3.7413 \times 10^5\text{ Pa}$। আংশিক চাপ $P_{\text{He}} = \frac{1.0}{1.5}P = 2.4942 \times 10^5\text{ Pa}$, $P_{\text{O}_2} = \frac{0.5}{1.5}P = 1.2471 \times 10^5\text{ Pa}$।</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 5</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>হিলিয়ামের আংশিক চাপ $P_{\text{He}} = 2.494 \times 10^5\text{ Pa}$, অক্সিজেনের $P_{\text{O}_2} = 1.247 \times 10^5\text{ Pa}$, মোট চাপ $P = 3.741 \times 10^5\text{ Pa} \approx 3.69\text{ atm}$</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3919,12 +3669,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>গ্যাসের ব্যাপন ও গ্রাহামের সূত্র (সমস্যা 6)</t>
+          <t>গ্যাস সূত্র ও হ্রদের বুদবুদ প্রসারণ (Gas Laws &amp; Lake Bubble Expansion)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -3932,25 +3682,25 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>[সমস্যা 6: গ্যাসের ব্যাপন ও গ্রাহামের সূত্র]
-একই তাপমাত্রা ও চাপে একটি সরু ছিদ্র দিয়ে অক্সিজেন গ্যাসের ব্যাপিত হতে $20\text{ s}$ সময় লাগে। সম-আয়তনের একটি অজানা গ্যাসের ব্যাপিত হতে $50\text{ s}$ সময় লাগলে অজানা গ্যাসটির আণবিক ভর কত?</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+একটি বেলুনে $20^\circ\text{C}$ তাপমাত্রায় এবং $1.0\text{ atm}$ চাপে $2.0\text{ m}^3$ হিলিয়াম গ্যাস রয়েছে। বেলুনটি এমন উচ্চতায় উঠল যেখানে চাপ $0.5\text{ atm}$ এবং তাপমাত্রা $-40^\circ\text{C}$। বেলুনটির নতুন আয়তন কত হবে?</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 6)।</t>
+          <t>$\frac{P_1 V_1}{T_1} = \frac{P_2 V_2}{T_2} \implies V_2 = V_1\left(\frac{P_1}{P_2}\right)\left(\frac{T_2}{T_1}\right)$। $T_1 = 273 + 20 = 293\text{ K}$, $T_2 = 273 - 40 = 233\text{ K}$। $V_2 = 2.0 \times \left(\frac{1.0}{0.5}\right) \times \left(\frac{233}{293}\right) = 4.0 \times 0.7952 \approx 3.181\text{ m}^3$।</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 6</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>নতুন আয়তন $V_2 = 3.18\text{ m}^3$</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3970,7 +3720,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>গ্যাসের গড় মুক্ত পথ (সমস্যা 7)</t>
+          <t>গ্যাস সূত্র ও হ্রদের বুদবুদ প্রসারণ (Gas Laws &amp; Lake Bubble Expansion)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3979,29 +3729,29 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>[সমস্যা 7: গ্যাসের গড় মুক্ত পথ]
-অক্সিজেন গ্যাসের অণুর ব্যাস $d = 3 \times 10^{-10}\text{ m}$ এবং প্রতি ঘনমিটারে অণুর সংখ্যা $n = 3 \times 10^{25}\text{ m}^{-3}$ হলে অণুগুলোর গড় মুক্ত পথ ($\lambda = \frac{1}{\sqrt{2}\pi n d^2}$) কত?</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##
+একটি বন্ধ পাত্রে সমান ভরের অক্সিজেন ($M = 32$) এবং নাইট্রোজেন ($M = 28$) গ্যাস মিশ্রিত আছে। মিশ্রণে অক্সিজেন ও নাইট্রোজেনের আংশিক চাপের অনুপাত $P_{	ext{O}_2} : P_{	ext{N}_2}$ কত?</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 7)।</t>
+          <t>উভয়ের ভর $m$ হলে অক্সিজেনের মোল $n_{\text{O}_2} = m/32$ এবং নাইট্রোজেনের মোল $n_{\text{N}_2} = m/28$। আংশিক চাপের অনুপাত মোল সংখ্যার অনুপাতের সমান: $\frac{P_{\text{O}_2}}{P_{\text{N}_2}} = \frac{n_{\text{O}_2}}{n_{\text{N}_2}} = \frac{m/32}{m/28} = \frac{28}{32} = \frac{7}{8} = 0.875$।</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 7</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>$P_{\text{O}_2} : P_{\text{N}_2} = 7 : 8 = 0.875$</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4021,12 +3771,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ভ্যান ডার ওয়ালস বাস্তব গ্যাস (সমস্যা 8)</t>
+          <t>গ্যাস সূত্র ও হ্রদের বুদবুদ প্রসারণ (Gas Laws &amp; Lake Bubble Expansion)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -4034,25 +3784,25 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>[সমস্যা 8: ভ্যান ডার ওয়ালস বাস্তব গ্যাস]
-$1\text{ mol}$ কার্বন ডাই-অক্সাইড গ্যাসের জন্য ভ্যান ডার ওয়ালস ধ্রুবক $a = 0.36\text{ N}\cdot\text{m}^4/\text{mol}^2$ এবং $b = 4.3 \times 10^{-5}\text{ m}^3/\text{mol}$ হলে এর মাত্রাগত তাৎপর্য ব্যাখ্যা কর।</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি পাম্প দ্বারা একটি সাইকেলের চাকায় বাতাস দেওয়া হচ্ছে। চাকার আয়তন $2.0\text{ L}$ স্থির থাকে এবং প্রারম্ভিক চাপ $1.0\text{ atm}$। প্রতিটি স্ট্রোকে পাম্পটি $1.0\text{ atm}$ চাপে $0.2\text{ L}$ বাতাস চাকার ভেতর প্রবেশ করালে কতটি স্ট্রোকের পর চাকার ভেতরের চাপ $3.5\text{ atm}$ হবে? (তাপমাত্রা অপরিবর্তিত)।</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 8)।</t>
+          <t>চাকার প্রারম্ভিক বাতাস $P_0 V_0 = 1.0 \times 2.0 = 2.0\text{ L}\cdot\text{atm}$। অন্তিম অবস্থায় $P V_0 = 3.5 \times 2.0 = 7.0\text{ L}\cdot\text{atm}$। প্রবেশকৃত মোট বাতাসের পরিমাণ $= 7.0 - 2.0 = 5.0\text{ L}\cdot\text{atm}$। প্রতি স্ট্রোকে প্রবেশ করে $0.2 \times 1.0 = 0.2\text{ L}\cdot\text{atm}$। অতএব স্ট্রোক সংখ্যা $N = \frac{5.0}{0.2} = 25$।</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 8</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>মোট $25$টি স্ট্রোক প্রয়োজন</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4072,7 +3822,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>মিশ্র গ্যাসের মোট চাপ (ডাল্টনের সূত্র) (সমস্যা 9)</t>
+          <t>গ্যাস সূত্র ও হ্রদের বুদবুদ প্রসারণ (Gas Laws &amp; Lake Bubble Expansion)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4081,29 +3831,29 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>[সমস্যা 9: মিশ্র গ্যাসের মোট চাপ (ডাল্টনের সূত্র)]
-$V_1 = 2\text{ L}$ আয়তনের পাত্রে $P_1 = 5\text{ atm}$ চাপে অক্সিজেন এবং $V_2 = 3\text{ L}$ আয়তনের পাত্রে $P_2 = 11\text{ atm}$ চাপে নাইট্রোজেন গ্যাস নিয়ে যুক্ত করলে মিশ্রণের মোট চাপ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ফাঁপা ধাতব গোলকের ওজন বায়ুতে $w_1$ এবং পানিতে নিমজ্জিত অবস্থায় $w_2$। গোলকটিতে কিছু গ্যাস ভরা হলে চাপ দ্বিগুণ হয়। আদর্শ গ্যাস আচরণ ধরে গ্যাসের ঘনত্ব ও আয়তনের সম্পর্ক প্রমাণ কর।</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 9)।</t>
+          <t>আর্কিমিডিসের নীতি অনুসারে অপসারিত পানির ওজনই প্লবতা $V = \frac{w_1 - w_2}{\rho_w g}$। গ্যাসের চাপ দ্বিগুণ হলে ঘনত্বও দ্বিগুণ হয়: $\rho_g' = 2\rho_g$ কারণ $\rho = \frac{PM}{RT} \propto P$।</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 9</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>প্লবতা $F_B = w_1 - w_2 = V \rho_{\text{water}} g$, গ্যাস ঘনত্ব $\rho_{\text{gas}} = \frac{PM}{RT}$</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4123,12 +3873,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>পরম শূন্য তাপমাত্রা ও গ্যাস সিলিন্ডার (সমস্যা 10)</t>
+          <t>গ্যাস সূত্র ও হ্রদের বুদবুদ প্রসারণ (Gas Laws &amp; Lake Bubble Expansion)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -4136,25 +3886,25 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>[সমস্যা 10: পরম শূন্য তাপমাত্রা ও গ্যাস সিলিন্ডার]
-একটি স্টিল সিলিন্ডারে $67^\circ\text{C}$ তাপমাত্রায় $P = 3\text{ atm}$ চাপে গ্যাস রক্ষিত আছে। তাপমাত্রা বৃদ্ধি পেয়ে $147^\circ\text{C}$ হলে সিলিন্ডারের অভ্যন্তরীণ চাপ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+একটি হ্রদের তলদেশে বাতাসের বুদবুদের ব্যাসার্ধ পৃষ্ঠে আসার পর দ্বিগুণ হয়। বায়ুমণ্ডলীয় চাপ $76\text{ cm-Hg}$ এবং পারদের ঘনত্ব $13.6\times 10^3\text{ kg/m}^3$ হলে হ্রদের গভীরতা কত? (উভয় স্থানে তাপমাত্রা সমান)।</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 10)।</t>
+          <t>ব্যাসার্ধ দ্বিগুণ হলে আয়তন $V \propto r^3$ অনুসারে $2^3 = 8$ গুণ হয় ($V_2 = 8V_1$)। তাপমাত্রা স্থির থাকায় বয়েলের সূত্র: $P_1 V_1 = P_2 V_2 \implies (P_0 + h\rho_w g)V_1 = P_0 (8V_1) \implies h\rho_w g = 7P_0$। বায়ুমণ্ডলীয় চাপ $P_0 = h_0 \rho_{\text{Hg}} g = 0.76 \times 13600 \times 9.8 = 101292.8\text{ Pa}$। গভীরতা $h = \frac{7 P_0}{\rho_w g} = \frac{7 \times 101292.8}{1000 \times 9.8} = \frac{709049.6}{9800} \approx 72.35\text{ m}$।</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 10</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>হ্রদের গভীরতা $h = 72.35\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4174,43 +3924,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>হ্রদের গভীরতা ও বুদবুদ প্রসারণ (সমস্যা 11)</t>
+          <t>আণবিক গতিতত্ত্ব, RMS বেগ ও শক্তি (Kinetic Theory, RMS Speed &amp; Energy)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>[সমস্যা 11: হ্রদের গভীরতা ও বুদবুদ প্রসারণ]
-##PRESET:pv-diagram(isothermal)[size:medium]##
-একটি হ্রদের তলদেশ হতে একটি বায়ুর বুদবুদ পানির উপরিপৃষ্ঠে উঠে আসায় এর আয়তন 7 গুণ হয়। বায়ুমণ্ডলীয় চাপ $1.013 \times 10^5\text{ Pa}$, পানির ঘনত্ব $1000\text{ kg/m}^3$, এবং তাপমাত্রা ধ্রুব থাকলে হ্রদের গভীরতা কত? ($g = 9.8\text{ m/s}^2$)</t>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+NTP-তে ($T = 273.15\text{ K}$) হাইড্রোজেন ($M = 2.0\text{ g/mol}$) এবং অক্সিজেন ($M = 32.0\text{ g/mol}$) অণুর বর্গমূল গড় বর্গ বেগ ($c_{	ext{rms}}$) নির্ণয় কর। কত তাপমাত্রায় অক্সিজেনের RMS বেগ NTP-তে হাইড্রোজেনের RMS বেগের সমান হবে? ($R = 8.314\text{ J/mol}\cdot\text{K}$)।</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>##PRESET:pv-diagram(isothermal)[size:medium]##</t>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 11)।</t>
+          <t>$c_{\text{rms}} = \sqrt{\frac{3RT}{M}}$। হাইড্রোজেনের জন্য ($M = 2 \times 10^{-3}\text{ kg/mol}$): $c_{\text{H}_2} = \sqrt{\frac{3(8.314)(273.15)}{0.002}} = \sqrt{3406834.7} \approx 1845.76\text{ m/s}$। অক্সিজেনের জন্য ($M = 32 \times 10^{-3}\text{ kg/mol}$): $c_{\text{O}_2} = \sqrt{\frac{3(8.314)(273.15)}{0.032}} = \frac{1845.76}{4} \approx 461.44\text{ m/s}$। সমান হওয়ার শর্ত: $\sqrt{\frac{3RT_2}{M_{\text{O}_2}}} = \sqrt{\frac{3RT_1}{M_{\text{H}_2}}} \implies \frac{T_2}{32} = \frac{273.15}{2} \implies T_2 = 273.15 \times 16 = 4370.4\text{ K}$।</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 11</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>$c_{\text{rms}}(\text{H}_2) = 1845.6\text{ m/s}, c_{\text{rms}}(\text{O}_2) = 461.4\text{ m/s}$, প্রয়োজনীয় তাপমাত্রা $T = 4370.4\text{ K} = 4097.25^\circ\text{C}$</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4230,7 +3975,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>গ্যাসের অণুর আরএমএস বেগ (সমস্যা 12)</t>
+          <t>আণবিক গতিতত্ত্ব, RMS বেগ ও শক্তি (Kinetic Theory, RMS Speed &amp; Energy)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4243,30 +3988,26 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>[সমস্যা 12: গ্যাসের অণুর আরএমএস বেগ]
-##PRESET:maxwell-distribution[size:medium]##
-$27^\circ\text{C}$ তাপমাত্রায় নাইট্রোজেন ($N_2$) গ্যাসের অণুর মূল গড় বর্গবেগ ($c_{rms} = \sqrt{\frac{3RT}{M}}$) কত নির্ণয় কর। ($R = 8.314\text{ J/(mol}\cdot\text{K)}, M = 28 \times 10^{-3}\text{ kg/mol}$)</t>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##
+একটি আদর্শ গ্যাসের চাপ $P = 1.0 	imes 10^5\text{ Pa}$ এবং ঘনত্ব $+ho = 1.25\text{ kg/m}^3$। গ্যাসের অণুগুলোর RMS বেগ নির্ণয় কর। প্রতি একক আয়তনে অণুগুলোর মোট রৈখিক গতিশক্তি কত?</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>##PRESET:maxwell-distribution[size:medium]##</t>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 12)।</t>
+          <t>চাপ $P = \frac{1}{3}\rho c_{\text{rms}}^2 \implies c_{\text{rms}} = \sqrt{\frac{3P}{\rho}} = \sqrt{\frac{3 \times 10^5}{1.25}} = \sqrt{240000} \approx 489.90\text{ m/s}$। প্রতি একক আয়তনের গতিশক্তি $E_V = \frac{1}{2}\rho c_{\text{rms}}^2 = \frac{3}{2}P = 1.5 \times 10^5\text{ J/m}^3$।</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 12</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>RMS বেগ $c = 489.9\text{ m/s}$, একক আয়তনে গতিশক্তি $E_V = 1.5 \times 10^5\text{ J/m}^3$</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4286,38 +4027,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>আপেক্ষিক আর্দ্রতা ও শিশিরাংক (সমস্যা 13)</t>
+          <t>আণবিক গতিতত্ত্ব, RMS বেগ ও শক্তি (Kinetic Theory, RMS Speed &amp; Energy)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>[সমস্যা 13: আপেক্ষিক আর্দ্রতা ও শিশিরাংক]
-কোনো একদিন বায়ুর তাপমাত্রা $30^\circ\text{C}$ এবং শিশিরাংক $9^\circ\text{C}$। $9^\circ\text{C}$ ও $30^\circ\text{C}$-এ সম্পৃক্ত জলীয় বাষ্পের চাপ যথাক্রমে $9.2\text{ mm-Hg}$ এবং $17.5\text{ mm-Hg}$ হলে ঐ দিনের আপেক্ষিক আর্দ্রতা কত?</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##
+একটি পাত্রে $27^\circ\text{C}$ তাপমাত্রায় $2.0\text{ মোল}$ নাইট্রোজেন গ্যাস ($N_2$, দ্বিপরমাণুক, $f = 5$) আবদ্ধ আছে। বোল্টজম্যান ধ্রুবক $k_B = 1.38 	imes 10^{-23}\text{ J/K}$ এবং অ্যাভোগাড্রো সংখ্যা $N_A = 6.022 	imes 10^{23}\text{ mol}^{-1}$ হলে: (ক) একটি অণুর গড় স্থানান্তরীয় গতিশক্তি, (খ) একটি অণুর মোট গতিশক্তি এবং (গ) সম্পূর্ণ গ্যাসের মোট অভ্যন্তরীণ শক্তি নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 13)।</t>
+          <t>(ক) স্থানান্তরীয় গতিশক্তি (৩টি স্বাধীনতার মাত্রা): $E_{tr} = \frac{3}{2}k_B T = 1.5(1.38 \times 10^{-23})(300) = 6.21 \times 10^{-21}\text{ J}$। (খ) মোট গতিশক্তি ($f = 5$ মাত্রা): $E = \frac{5}{2}k_B T = 2.5(1.38 \times 10^{-23})(300) = 1.035 \times 10^{-20}\text{ J}$। (গ) $n = 2$ মোলের অভ্যন্তরীণ শক্তি $U = n \frac{f}{2} R T = 2 \times \frac{5}{2}(8.314)(300) = 5 \times 8.314 \times 300 = 12471.0\text{ J}$।</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 13</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>(ক) স্থানান্তরীয় $E_{tr} = 6.21 \times 10^{-21}\text{ J}$, (খ) মোট প্রতি অণু $E_{\text{total}} = 1.035 \times 10^{-20}\text{ J}$, (গ) মোট অভ্যন্তরীণ শক্তি $U = 12471.0\text{ J} \approx 12.47\text{ kJ}$</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4337,7 +4078,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>গ্যাসের মোট গতিশক্তি ও চাপ (সমস্যা 14)</t>
+          <t>আণবিক গতিতত্ত্ব, RMS বেগ ও শক্তি (Kinetic Theory, RMS Speed &amp; Energy)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4350,25 +4091,25 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>[সমস্যা 14: গ্যাসের মোট গতিশক্তি ও চাপ]
-একটি $V = 4\text{ m}^3$ আয়তনের পাত্রে $P = 11 \times 10^5\text{ Pa}$ চাপে গ্যাস আবদ্ধ আছে। পাত্রে রক্ষিত সমগ্র গ্যাসের মোট গতিশক্তি ($E_k = \frac{3}{2}PV$) কত জুল?</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+একটি হিলিয়াম পরমাণুর ভর $m = 6.64 	imes 10^{-27}\text{ kg}$। কত তাপমাত্রায় হিলিয়াম পরমাণুর RMS বেগ পৃথিবীর মুক্তিবেগের ($v_e = 11.2\text{ km/s}$) সমান হবে?</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 14)।</t>
+          <t>RMS বেগ $c = \sqrt{\frac{3k_B T}{m}} = v_e \implies \frac{3k_B T}{m} = v_e^2 \implies T = \frac{m v_e^2}{3k_B}$। মান বসিয়ে: $T = \frac{(6.64 \times 10^{-27})(11200)^2}{3(1.38 \times 10^{-23})} = \frac{6.64 \times 10^{-27} \times 1.2544 \times 10^8}{4.14 \times 10^{-23}} = \frac{8.3292 \times 10^{-19}}{4.14 \times 10^{-23}} \approx 20118.8\text{ K}$। ($R$ ভিত্তিক: $M = 4 \times 10^{-3}\text{ kg/mol} \implies T = \frac{0.004 \times (11200)^2}{3 \times 8.314} = \frac{501760}{24.942} \approx 20117.0\text{ K}$)।</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 14</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>প্রয়োজনীয় তাপমাত্রা $T = 20042.8\text{ K}$</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4388,38 +4129,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>স্বাধীনতার মাত্রা ও মোলার তাপধারণ ক্ষমতা (সমস্যা 15)</t>
+          <t>আণবিক গতিতত্ত্ব, RMS বেগ ও শক্তি (Kinetic Theory, RMS Speed &amp; Energy)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>[সমস্যা 15: স্বাধীনতার মাত্রা ও মোলার তাপধারণ ক্ষমতা]
-একটি দ্বি-পরমাণুক আদর্শ গ্যাসের স্বাধীনতার মাত্রা $f = 5$ হলে গ্যাসটির স্থির চাপে ও স্থির আয়তনে মোলার আপেক্ষিক তাপদ্বয়ের অনুপাত $\gamma = C_p / C_v$ কত?</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+ম্যাক্সওয়েলের আণবিক বেগ বণ্টন সূত্রে কোনো গ্যাসে সর্বাধিক সম্ভাব্য বেগ $c_p$, গড় বেগ $\bar{c}$ এবং RMS বেগ $c_{\text{rms}}$-এর অনুপাত কত? এদের মান যথাক্রমে $c_p : \bar{c} : c_{\text{rms}} = \sqrt{2} : \sqrt{8/\pi} : \sqrt{3}$ প্রমাণ কর।</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 15)।</t>
+          <t>সর্বাধিক সম্ভাব্য বেগ $c_p = \sqrt{\frac{2RT}{M}}$। গড় বেগ $\bar{c} = \sqrt{\frac{8RT}{\pi M}}$। RMS বেগ $c_{\text{rms}} = \sqrt{\frac{3RT}{M}}$। অনুপাত $= \sqrt{2} : \sqrt{\frac{8}{\pi}} : \sqrt{3} \approx 1.414 : 1.596 : 1.732 = 1 : 1.128 : 1.225$।</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 15</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>$c_p : \bar{c} : c_{\text{rms}} = 1 : 1.128 : 1.225 = \sqrt{2} : \sqrt{8/\pi} : \sqrt{3}$</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4439,7 +4180,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>গ্যাসের ব্যাপন ও গ্রাহামের সূত্র (সমস্যা 16)</t>
+          <t>আণবিক গতিতত্ত্ব, RMS বেগ ও শক্তি (Kinetic Theory, RMS Speed &amp; Energy)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4452,25 +4193,25 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>[সমস্যা 16: গ্যাসের ব্যাপন ও গ্রাহামের সূত্র]
-একই তাপমাত্রা ও চাপে একটি সরু ছিদ্র দিয়ে অক্সিজেন গ্যাসের ব্যাপিত হতে $60\text{ s}$ সময় লাগে। সম-আয়তনের একটি অজানা গ্যাসের ব্যাপিত হতে $50\text{ s}$ সময় লাগলে অজানা গ্যাসটির আণবিক ভর কত?</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি গ্যাসে অণুগুলোর গতিবেগ যথাক্রমে $1\text{ m/s}, 2\text{ m/s}, 3\text{ m/s}, 4\text{ m/s}, 5\text{ m/s}$। এই ৫টি অণুর গড় বেগ $\bar{c}$ এবং RMS বেগ $c_{\text{rms}}$ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 16)।</t>
+          <t>গড় বেগ $\bar{c} = \frac{1+2+3+4+5}{5} = \frac{15}{5} = 3.0\text{ m/s}$। বেগের বর্গের গড় $\overline{c^2} = \frac{1^2+2^2+3^2+4^2+5^2}{5} = \frac{1+4+9+16+25}{5} = \frac{55}{5} = 11.0\text{ m}^2/\text{s}^2$। RMS বেগ $c_{\text{rms}} = \sqrt{\overline{c^2}} = \sqrt{11} \approx 3.3166\text{ m/s}$। লক্ষণীয় $c_{\text{rms}} &gt; \bar{c}$।</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 16</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>গড় বেগ $\bar{c} = 3.0\text{ m/s}$, RMS বেগ $c_{\text{rms}} = 3.317\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4490,38 +4231,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>গ্যাসের গড় মুক্ত পথ (সমস্যা 17)</t>
+          <t>আণবিক গতিতত্ত্ব, RMS বেগ ও শক্তি (Kinetic Theory, RMS Speed &amp; Energy)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>[সমস্যা 17: গ্যাসের গড় মুক্ত পথ]
-অক্সিজেন গ্যাসের অণুর ব্যাস $d = 3 \times 10^{-10}\text{ m}$ এবং প্রতি ঘনমিটারে অণুর সংখ্যা $n = 7 \times 10^{25}\text{ m}^{-3}$ হলে অণুগুলোর গড় মুক্ত পথ ($\lambda = \frac{1}{\sqrt{2}\pi n d^2}$) কত?</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+একটি আবদ্ধ পাত্রে নির্দিষ্ট ভরের গ্যাসের পরম তাপমাত্রা $4$ গুণ করা হলে অণুগুলোর RMS বেগ কত গুণ হবে এবং গ্যাসের চাপ কত গুণ হবে? (আয়তন স্থির)।</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 17)।</t>
+          <t>RMS বেগ $c \propto \sqrt{T}$। তাপমাত্রা ৪ গুণ হলে নতুন বেগ $c' = \sqrt{4}c = 2c$ (দ্বিগুণ)। চাপ $P \propto T$ (আয়তন স্থির থাকায় গে-লুসাকের সূত্র অনুসারে) অথবা $P \propto c^2 \propto 2^2 = 4$ গুণ বৃদ্ধি পাবে।</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 17</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>RMS বেগ $2.0$ গুণ হবে, চাপ $4.0$ গুণ হবে</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4541,7 +4282,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ভ্যান ডার ওয়ালস বাস্তব গ্যাস (সমস্যা 18)</t>
+          <t>আণবিক গতিতত্ত্ব, RMS বেগ ও শক্তি (Kinetic Theory, RMS Speed &amp; Energy)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4554,25 +4295,25 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>[সমস্যা 18: ভ্যান ডার ওয়ালস বাস্তব গ্যাস]
-$1\text{ mol}$ কার্বন ডাই-অক্সাইড গ্যাসের জন্য ভ্যান ডার ওয়ালস ধ্রুবক $a = 0.36\text{ N}\cdot\text{m}^4/\text{mol}^2$ এবং $b = 4.3 \times 10^{-5}\text{ m}^3/\text{mol}$ হলে এর মাত্রাগত তাৎপর্য ব্যাখ্যা কর।</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+স্বাভাবিক তাপমাত্রা ও চাপে ($0^\circ\text{C}, 1.013 \times 10^5\text{ Pa}$) বাতাসের ঘনত্ব $1.29\text{ kg/m}^3$। বাতাসের অণুগুলোর RMS বেগ এবং গড় গতিশক্তি নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 18)।</t>
+          <t>$c_{\text{rms}} = \sqrt{\frac{3P}{\rho}} = \sqrt{\frac{3 \times 1.013 \times 10^5}{1.29}} = \sqrt{\frac{303900}{1.29}} = \sqrt{235581.4} \approx 485.37\text{ m/s}$। প্রতি একক ভরের গতিশক্তি $\frac{1}{2}c_{\text{rms}}^2 = 0.5(235581.4) \approx 1.178 \times 10^5\text{ J/kg}$।</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 18</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>RMS বেগ $c_{\text{rms}} = 485.4\text{ m/s}$, প্রতি একক ভরের গতিশক্তি $E_m = 1.178 \times 10^5\text{ J/kg}$</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4592,38 +4333,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>মিশ্র গ্যাসের মোট চাপ (ডাল্টনের সূত্র) (সমস্যা 19)</t>
+          <t>আণবিক গতিতত্ত্ব, RMS বেগ ও শক্তি (Kinetic Theory, RMS Speed &amp; Energy)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>[সমস্যা 19: মিশ্র গ্যাসের মোট চাপ (ডাল্টনের সূত্র)]
-$V_1 = 2\text{ L}$ আয়তনের পাত্রে $P_1 = 3\text{ atm}$ চাপে অক্সিজেন এবং $V_2 = 3\text{ L}$ আয়তনের পাত্রে $P_2 = 11\text{ atm}$ চাপে নাইট্রোজেন গ্যাস নিয়ে যুক্ত করলে মিশ্রণের মোট চাপ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2.5,h=4][size:small]##
+একটি গ্যাস মিশ্রণে $28\text{ g}$ নাইট্রোজেন এবং $64\text{ g}$ অক্সিজেন রয়েছে। গ্যাস অণুগুলোর মোট গতিশক্তি $300\text{ K}$ তাপমাত্রায় কত জুল হবে? (উভয় গ্যাসকে অনমনীয় দ্বিপরমাণুক $f = 5$ ধর)।</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2.5,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 19)।</t>
+          <t>নাইট্রোজেনের মোল $n_1 = \frac{28}{28} = 1.0\text{ mol}$। অক্সিজেনের মোল $n_2 = \frac{64}{32} = 2.0\text{ mol}$। মোট মোল $n = 3.0\text{ mol}$। মোট গতিশক্তি $U = n \frac{5}{2} R T = 3.0 \times 2.5 \times 8.314 \times 300 = 7.5 \times 2494.2 = 18706.5\text{ J}$।</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 19</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>মোট অভ্যন্তরীণ গতিশক্তি $U = 18706.5\text{ J} = 18.71\text{ kJ}$</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4643,7 +4384,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>পরম শূন্য তাপমাত্রা ও গ্যাস সিলিন্ডার (সমস্যা 20)</t>
+          <t>আণবিক গতিতত্ত্ব, RMS বেগ ও শক্তি (Kinetic Theory, RMS Speed &amp; Energy)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4656,25 +4397,25 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>[সমস্যা 20: পরম শূন্য তাপমাত্রা ও গ্যাস সিলিন্ডার]
-একটি স্টিল সিলিন্ডারে $47^\circ\text{C}$ তাপমাত্রায় $P = 3\text{ atm}$ চাপে গ্যাস রক্ষিত আছে। তাপমাত্রা বৃদ্ধি পেয়ে $127^\circ\text{C}$ হলে সিলিন্ডারের অভ্যন্তরীণ চাপ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+কোন তাপমাত্রায় নাইট্রোজেন অণুর RMS বেগ $0^\circ\text{C}$ তাপমাত্রার RMS বেগের দ্বিগুণ হবে?</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 20)।</t>
+          <t>$c \propto \sqrt{T} \implies \frac{c_2}{c_1} = \sqrt{\frac{T_2}{T_1}} = 2 \implies \frac{T_2}{T_1} = 4 \implies T_2 = 4 T_1 = 4(273.15) = 1092.6\text{ K}$। সেলসিয়াসে $\theta_2 = 1092.6 - 273.15 = 819.45^\circ\text{C}$।</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 20</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>তাপমাত্রা $T_2 = 1092.6\text{ K} = 819.45^\circ\text{C}$</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4694,43 +4435,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>হ্রদের গভীরতা ও বুদবুদ প্রসারণ (সমস্যা 21)</t>
+          <t>গড় মুক্ত পথ ও আণবিক সংঘর্ষ (Mean Free Path &amp; Molecular Collisions)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>[সমস্যা 21: হ্রদের গভীরতা ও বুদবুদ প্রসারণ]
-##PRESET:pv-diagram(isothermal)[size:medium]##
-একটি হ্রদের তলদেশ হতে একটি বায়ুর বুদবুদ পানির উপরিপৃষ্ঠে উঠে আসায় এর আয়তন 5 গুণ হয়। বায়ুমণ্ডলীয় চাপ $1.013 \times 10^5\text{ Pa}$, পানির ঘনত্ব $1000\text{ kg/m}^3$, এবং তাপমাত্রা ধ্রুব থাকলে হ্রদের গভীরতা কত? ($g = 9.8\text{ m/s}^2$)</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+স্বাভাবিক তাপমাত্রা ও চাপে (NTP) প্রতি ঘনমিটারে বাতাসের অণুর সংখ্যা $n = 2.69 \times 10^{25}\text{ m}^{-3}$। অক্সিজেন অণুর কার্যকর ব্যাস $d = 3.0 \times 10^{-10}\text{ m}$ (বা $3.0\text{ Å}$) হলে ক্লসিয়াসের এবং ম্যাক্সওয়েলের সূত্র অনুসারে অণুর গড় মুক্ত পথ (Mean Free Path $\lambda$) নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>##PRESET:pv-diagram(isothermal)[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 21)।</t>
+          <t>ম্যাক্সওয়েলের নিখুঁত সমীকরণ: $\lambda = \frac{1}{\sqrt{2}\pi n d^2} = \frac{1}{\sqrt{2}\pi (2.69 \times 10^{25})(3.0 \times 10^{-10})^2} = \frac{1}{1.4142 \times 3.1416 \times 2.69 \times 10^{25} \times 9 \times 10^{-20}} = \frac{1}{1.0754 \times 10^7} \approx 9.30 \times 10^{-8}\text{ m} = 93.0\text{ nm}$। ক্লসিয়াসের সমীকরণ: $\lambda_C = \frac{1}{\pi n d^2} = \sqrt{2}\lambda \approx 1.315 \times 10^{-7}\text{ m}$।</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 21</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>ম্যাক্সওয়েলের সূত্রানুযায়ী $\lambda = 9.30 \times 10^{-8}\text{ m} = 93.0\text{ nm}$, ক্লসিয়াসের $\lambda_C = 1.315 \times 10^{-7}\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4750,12 +4486,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>গ্যাসের অণুর আরএমএস বেগ (সমস্যা 22)</t>
+          <t>গড় মুক্ত পথ ও আণবিক সংঘর্ষ (Mean Free Path &amp; Molecular Collisions)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -4763,30 +4499,25 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>[সমস্যা 22: গ্যাসের অণুর আরএমএস বেগ]
-##PRESET:maxwell-distribution[size:medium]##
-$67^\circ\text{C}$ তাপমাত্রায় নাইট্রোজেন ($N_2$) গ্যাসের অণুর মূল গড় বর্গবেগ ($c_{rms} = \sqrt{\frac{3RT}{M}}$) কত নির্ণয় কর। ($R = 8.314\text{ J/(mol}\cdot\text{K)}, M = 28 \times 10^{-3}\text{ kg/mol}$)</t>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##
+একটি পাত্রে নির্দিষ্ট তাপমাত্রায় চাপ $10^{-4}\text{ mm-Hg}$ পর্যন্ত কমিয়ে উচ্চ শূন্যতা (Vacuum) সৃষ্টি করা হলো। স্বাভাবিক চাপে ($760\text{ mm-Hg}$) গ্যাসের গড় মুক্ত পথ $\lambda_0 = 1.0 \times 10^{-7}\text{ m}$ হলে এই নিম্ন চাপে অণুর গড় মুক্ত পথ কত মিটার হবে?</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>##PRESET:maxwell-distribution[size:medium]##</t>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 22)।</t>
+          <t>গড় মুক্ত পথ চাপের ব্যস্তানুপাতিক ($\lambda \propto 1/P$ কারণ $n = P/k_B T \implies \lambda \propto 1/n \propto 1/P$)। $\frac{\lambda}{\lambda_0} = \frac{P_0}{P} = \frac{760}{10^{-4}} = 7.6 \times 10^6$। অতএব $\lambda = (1.0 \times 10^{-7}\text{ m}) \times (7.6 \times 10^6) = 0.76\text{ m}$।</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 22</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>নতুন গড় মুক্ত পথ $\lambda = 0.76\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4806,38 +4537,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>আপেক্ষিক আর্দ্রতা ও শিশিরাংক (সমস্যা 23)</t>
+          <t>গড় মুক্ত পথ ও আণবিক সংঘর্ষ (Mean Free Path &amp; Molecular Collisions)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>[সমস্যা 23: আপেক্ষিক আর্দ্রতা ও শিশিরাংক]
-কোনো একদিন বায়ুর তাপমাত্রা $70^\circ\text{C}$ এবং শিশিরাংক $9^\circ\text{C}$। $9^\circ\text{C}$ ও $70^\circ\text{C}$-এ সম্পৃক্ত জলীয় বাষ্পের চাপ যথাক্রমে $9.2\text{ mm-Hg}$ এবং $17.5\text{ mm-Hg}$ হলে ঐ দিনের আপেক্ষিক আর্দ্রতা কত?</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি গ্যাসের অণুর ব্যাস $d = 2.0 \times 10^{-10}\text{ m}$ এবং প্রতি ঘনমিটারে অণু সংখ্যা $n = 3.0 \times 10^{25}\text{ m}^{-3}$। অণুগুলোর গড় দ্রুতি $\bar{c} = 500\text{ m/s}$ হলে (ক) গড় মুক্ত পথ এবং (খ) প্রতি সেকেন্ডে একটি অণুর সংঘর্ষ সংখ্যা (Collision frequency $\nu$) নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 23)।</t>
+          <t>(ক) ম্যাক্সওয়েলের সূত্র: $\lambda = \frac{1}{\sqrt{2}\pi n d^2} = \frac{1}{1.4142 \times \pi \times (3 \times 10^{25}) \times (4 \times 10^{-20})} = \frac{1}{5.331 \times 10^6} \approx 1.876 \times 10^{-7}\text{ m}$। (খ) প্রতি সেকেন্ডে সংঘর্ষ সংখ্যা $\nu = \frac{\bar{c}}{\lambda} = \frac{500}{1.876 \times 10^{-7}} \approx 2.665 \times 10^9\text{ s}^{-1}$ (প্রতি সেকেন্ডে প্রায় ২৬৬.৫ কোটি বার)।</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 23</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>(ক) $\lambda = 1.876 \times 10^{-7}\text{ m}$, (খ) সংঘর্ষ কম্পাঙ্ক $\nu = 2.665 \times 10^9\text{ s}^{-1}$</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4857,12 +4588,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>গ্যাসের মোট গতিশক্তি ও চাপ (সমস্যা 24)</t>
+          <t>গড় মুক্ত পথ ও আণবিক সংঘর্ষ (Mean Free Path &amp; Molecular Collisions)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -4870,25 +4601,25 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>[সমস্যা 24: গ্যাসের মোট গতিশক্তি ও চাপ]
-একটি $V = 2\text{ m}^3$ আয়তনের পাত্রে $P = 11 \times 10^5\text{ Pa}$ চাপে গ্যাস আবদ্ধ আছে। পাত্রে রক্ষিত সমগ্র গ্যাসের মোট গতিশক্তি ($E_k = \frac{3}{2}PV$) কত জুল?</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##
+একটি আবদ্ধ পাত্রের আয়তন অপরিবর্তিত রেখে তাপমাত্রা দ্বিগুণ করা হলো। গ্যাসের গড় মুক্ত পথ $\lambda$ এবং সংঘর্ষ কম্পাঙ্কের কী পরিবর্তন ঘটবে?</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 24)।</t>
+          <t>পাত্র আবদ্ধ ও আয়তন স্থির থাকায় অণুর সংখ্যা ঘনত্ব $n = N/V$ স্থির থাকে। গড় মুক্ত পথ $\lambda = \frac{1}{\sqrt{2}\pi n d^2}$ কেবলমাত্র $n$ এবং $d$-এর ওপর নির্ভর করে; ফলে $\lambda$ সম্পূর্ণ অপরিবর্তিত থাকবে। তবে বেগ $\bar{c} \propto \sqrt{T}$ হওয়ায় তাপমাত্রা দ্বিগুণে বেগ $\sqrt{2}$ গুণ বৃদ্ধি পায়, ফলে সংঘর্ষ কম্পাঙ্ক $\nu = \bar{c}/\lambda$ ও $\sqrt{2}$ গুণ বৃদ্ধি পাবে।</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 24</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>গড় মুক্ত পথ $\lambda$ অপরিবর্তিত থাকবে, সংঘর্ষ কম্পাঙ্ক $\sqrt{2} \approx 1.414$ গুণ বৃদ্ধি পাবে</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4908,38 +4639,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>স্বাধীনতার মাত্রা ও মোলার তাপধারণ ক্ষমতা (সমস্যা 25)</t>
+          <t>গড় মুক্ত পথ ও আণবিক সংঘর্ষ (Mean Free Path &amp; Molecular Collisions)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>[সমস্যা 25: স্বাধীনতার মাত্রা ও মোলার তাপধারণ ক্ষমতা]
-একটি দ্বি-পরমাণুক আদর্শ গ্যাসের স্বাধীনতার মাত্রা $f = 5$ হলে গ্যাসটির স্থির চাপে ও স্থির আয়তনে মোলার আপেক্ষিক তাপদ্বয়ের অনুপাত $\gamma = C_p / C_v$ কত?</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##
+কোনো গ্যাসের চাপ স্থির রেখে তাপমাত্রা দ্বিগুণ করা হলে গ্যাসের গড় মুক্ত পথ পূর্বের কত গুণ হবে?</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 25)।</t>
+          <t>চাপ স্থির থাকলে $P = n k_B T \implies n \propto \frac{1}{T}$। তাপমাত্রা দ্বিগুণ হলে অণুর সংখ্যা ঘনত্ব $n$ অর্ধেক হয়ে যায়। অতএব গড় মুক্ত পথ $\lambda \propto \frac{1}{n} \propto T$ তাপমাত্রা দ্বিগুণ হওয়ায় দ্বিগুণ হবে।</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 25</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>গড় মুক্ত পথ $2.0$ গুণ বৃদ্ধি পাবে</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4959,12 +4690,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>গ্যাসের ব্যাপন ও গ্রাহামের সূত্র (সমস্যা 26)</t>
+          <t>গড় মুক্ত পথ ও আণবিক সংঘর্ষ (Mean Free Path &amp; Molecular Collisions)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -4972,25 +4703,25 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>[সমস্যা 26: গ্যাসের ব্যাপন ও গ্রাহামের সূত্র]
-একই তাপমাত্রা ও চাপে একটি সরু ছিদ্র দিয়ে অক্সিজেন গ্যাসের ব্যাপিত হতে $40\text{ s}$ সময় লাগে। সম-আয়তনের একটি অজানা গ্যাসের ব্যাপিত হতে $50\text{ s}$ সময় লাগলে অজানা গ্যাসটির আণবিক ভর কত?</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+দুটি গ্যাসের অণুর ব্যাসের অনুপাত $1:2$ এবং প্রতি একক আয়তনে অণু সংখ্যার অনুপাত $2:1$। গ্যাসদ্বয়ের গড় মুক্ত পথের অনুপাত $\lambda_1 : \lambda_2$ কত?</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 26)।</t>
+          <t>গড় মুক্ত পথ $\lambda \propto \frac{1}{n d^2}$। $\frac{\lambda_1}{\lambda_2} = \left(\frac{n_2}{n_1}\right)\left(\frac{d_2}{d_1}\right)^2 = \left(\frac{1}{2}\right)\left(\frac{2}{1}\right)^2 = \frac{1}{2} \times 4 = 2$। অতএব $\lambda_1 : \lambda_2 = 2 : 1$।</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 26</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>$\lambda_1 : \lambda_2 = 2 : 1$</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5010,38 +4741,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>গ্যাসের গড় মুক্ত পথ (সমস্যা 27)</t>
+          <t>গড় মুক্ত পথ ও আণবিক সংঘর্ষ (Mean Free Path &amp; Molecular Collisions)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>[সমস্যা 27: গ্যাসের গড় মুক্ত পথ]
-অক্সিজেন গ্যাসের অণুর ব্যাস $d = 3 \times 10^{-10}\text{ m}$ এবং প্রতি ঘনমিটারে অণুর সংখ্যা $n = 5 \times 10^{25}\text{ m}^{-3}$ হলে অণুগুলোর গড় মুক্ত পথ ($\lambda = \frac{1}{\sqrt{2}\pi n d^2}$) কত?</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##
+একটি আদর্শ গ্যাসের চাপ $1.0\text{ atm}$ এবং তাপমাত্রা $300\text{ K}$। অণুর কার্যকর ব্যাস $0.35\text{ nm}$ হলে প্রতি ঘনমিটারে অণু সংখ্যা $n$ এবং গড় মুক্ত পথ নির্ণয় কর। ($k_B = 1.38 	imes 10^{-23}\text{ J/K}$)।</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 27)।</t>
+          <t>চাপ $P = 1.013 \times 10^5\text{ Pa}$। অণু সংখ্যা ঘনত্ব $n = \frac{P}{k_B T} = \frac{1.013 \times 10^5}{(1.38 \times 10^{-23})(300)} = \frac{1.013 \times 10^5}{4.14 \times 10^{-21}} \approx 2.4468 \times 10^{25}\text{ m}^{-3}$। ব্যাস $d = 3.5 \times 10^{-10}\text{ m}$। গড় মুক্ত পথ $\lambda = \frac{1}{\sqrt{2}\pi n d^2} = \frac{1}{1.4142 \times \pi \times 2.4468 \times 10^{25} \times (1.225 \times 10^{-19})} = \frac{1}{1.332 \times 10^7} \approx 7.507 \times 10^{-8}\text{ m} \approx 75.1\text{ nm}$।</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 27</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+          <t>$n = 2.447 \times 10^{25}\text{ m}^{-3}, \lambda = 7.55 \times 10^{-8}\text{ m} = 75.5\text{ nm}$</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5061,12 +4792,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ভ্যান ডার ওয়ালস বাস্তব গ্যাস (সমস্যা 28)</t>
+          <t>গড় মুক্ত পথ ও আণবিক সংঘর্ষ (Mean Free Path &amp; Molecular Collisions)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -5074,25 +4805,25 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>[সমস্যা 28: ভ্যান ডার ওয়ালস বাস্তব গ্যাস]
-$1\text{ mol}$ কার্বন ডাই-অক্সাইড গ্যাসের জন্য ভ্যান ডার ওয়ালস ধ্রুবক $a = 0.36\text{ N}\cdot\text{m}^4/\text{mol}^2$ এবং $b = 4.3 \times 10^{-5}\text{ m}^3/\text{mol}$ হলে এর মাত্রাগত তাৎপর্য ব্যাখ্যা কর।</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি গ্যাস অণুর পরপর দুটি সংঘর্ষের মধ্যবর্তী গড় সময়কে শিথিলকরণ কাল (Relaxation time $\tau$) বলে। $300\text{ K}$ তাপমাত্রায় নাইট্রোজেনের জন্য $\lambda = 6.0 \times 10^{-8}\text{ m}$ এবং $\bar{c} = 475\text{ m/s}$ হলে শিথিলকরণ কাল $\tau$ কত সেকেন্ড?</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 28)।</t>
+          <t>শিথিলকরণ কাল $\tau = \frac{\lambda}{\bar{c}} = \frac{6.0 \times 10^{-8}\text{ m}}{475\text{ m/s}} \approx 1.263 \times 10^{-10}\text{ s} = 0.1263\text{ ns}$।</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 28</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+          <t>$\tau = 1.263 \times 10^{-10}\text{ s} = 0.126\text{ ns}$</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5112,38 +4843,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>মিশ্র গ্যাসের মোট চাপ (ডাল্টনের সূত্র) (সমস্যা 29)</t>
+          <t>গড় মুক্ত পথ ও আণবিক সংঘর্ষ (Mean Free Path &amp; Molecular Collisions)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>[সমস্যা 29: মিশ্র গ্যাসের মোট চাপ (ডাল্টনের সূত্র)]
-$V_1 = 2\text{ L}$ আয়তনের পাত্রে $P_1 = 7\text{ atm}$ চাপে অক্সিজেন এবং $V_2 = 3\text{ L}$ আয়তনের পাত্রে $P_2 = 11\text{ atm}$ চাপে নাইট্রোজেন গ্যাস নিয়ে যুক্ত করলে মিশ্রণের মোট চাপ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি অণুর ব্যাস $d$। অণুটির সংঘর্ষ প্রস্থচ্ছেদ (Collision cross-section $\sigma$) কত? যদি ব্যাস $20\%$ বৃদ্ধি পায়, তবে গড় মুক্ত পথ শতকরা কত হ্রাস পাবে?</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 29)।</t>
+          <t>সংঘর্ষ প্রস্থচ্ছেদ $\sigma = \pi d^2$। ব্যাস $d' = 1.20 d$ হলে নতুন প্রস্থচ্ছেদ $\sigma' = (1.20)^2 \sigma = 1.44 \sigma$। গড় মুক্ত পথ $\lambda \propto \frac{1}{\sigma}$ হওয়ায় নতুন মুক্ত পথ $\lambda' = \frac{\lambda}{1.44} \approx 0.6944\lambda$। শতকরা হ্রাস $= (1 - 0.6944) \times 100\% = 30.56\%$।</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 29</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>সংঘর্ষ প্রস্থচ্ছেদ $\sigma = \pi d^2$, গড় মুক্ত পথ হ্রাস পাবে $30.56\%$</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5163,12 +4894,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>পরম শূন্য তাপমাত্রা ও গ্যাস সিলিন্ডার (সমস্যা 30)</t>
+          <t>গড় মুক্ত পথ ও আণবিক সংঘর্ষ (Mean Free Path &amp; Molecular Collisions)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -5176,25 +4907,25 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>[সমস্যা 30: পরম শূন্য তাপমাত্রা ও গ্যাস সিলিন্ডার]
-একটি স্টিল সিলিন্ডারে $27^\circ\text{C}$ তাপমাত্রায় $P = 3\text{ atm}$ চাপে গ্যাস রক্ষিত আছে। তাপমাত্রা বৃদ্ধি পেয়ে $147^\circ\text{C}$ হলে সিলিন্ডারের অভ্যন্তরীণ চাপ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=2][size:small]##
+একটি পাত্রে হিলিয়াম গ্যাস রয়েছে। পাত্রের আয়তন সংকুচিত করে এক-চতুর্থাংশ ($V/4$) করা হলে এবং পরম তাপমাত্রা অপরিবর্তিত রাখা হলে গড় মুক্ত পথ এবং সংঘর্ষ হারের কীরূপ পরিবর্তন হবে?</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 30)।</t>
+          <t>আয়তন ১/৪ অংশ হলে অণু সংখ্যা ঘনত্ব $n = N/(V/4) = 4n$ (৪ গুণ)। গড় মুক্ত পথ $\lambda \propto 1/n$ হওয়ায় তা আদি মানের $\frac{1}{4}$ অংশে নেমে আসবে। তাপমাত্রা স্থির থাকায় বেগ $\bar{c}$ অপরিবর্তিত থাকে, ফলে সংঘর্ষ হার $\nu = \frac{\bar{c}}{\lambda} = 4 \nu_0$ (৪ গুণ হবে)।</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 30</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>গড় মুক্ত পথ $\frac{1}{4}$ অংশ হবে, সংঘর্ষের হার $4.0$ গুণ বৃদ্ধি পাবে</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5214,43 +4945,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>হ্রদের গভীরতা ও বুদবুদ প্রসারণ (সমস্যা 31)</t>
+          <t>আর্দ্রতা, শিশিরাংক ও গ্লেইশারের সূত্র (Humidity, Dew Point &amp; Glaisher Formula)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>[সমস্যা 31: হ্রদের গভীরতা ও বুদবুদ প্রসারণ]
-##PRESET:pv-diagram(isothermal)[size:medium]##
-একটি হ্রদের তলদেশ হতে একটি বায়ুর বুদবুদ পানির উপরিপৃষ্ঠে উঠে আসায় এর আয়তন 3 গুণ হয়। বায়ুমণ্ডলীয় চাপ $1.013 \times 10^5\text{ Pa}$, পানির ঘনত্ব $1000\text{ kg/m}^3$, এবং তাপমাত্রা ধ্রুব থাকলে হ্রদের গভীরতা কত? ($g = 9.8\text{ m/s}^2$)</t>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##
+কোনো একদিন বায়ুর তাপমাত্রা $\theta = 25^\circ\text{C}$ এবং শিশিরাংক $\theta_d = 12^\circ\text{C}$। $12^\circ\text{C}$ এবং $25^\circ\text{C}$ তাপমাত্রায় সম্পৃক্ত জলীয় বাষ্পচাপ যথাক্রমে $10.52\text{ mm-Hg}$ এবং $23.76\text{ mm-Hg}$। ওই দিনের আপেক্ষিক আর্দ্রতা (Relative Humidity $RH$) নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>##PRESET:pv-diagram(isothermal)[size:medium]##</t>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 31)।</t>
+          <t>আপেক্ষিক আর্দ্রতার সূত্র: $RH = \frac{f}{F} \times 100\%$। এখানে $f = $ শিশিরাংকে সম্পৃক্ত বাষ্পচাপ $= 10.52\text{ mm-Hg}$। $F = $ বায়ুর তাপমাত্রায় সম্পৃক্ত বাষ্পচাপ $= 23.76\text{ mm-Hg}$। $RH = \frac{10.52}{23.76} \times 100\% \approx 44.276\% \approx 44.28\%$।</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 31</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>আপেক্ষিক আর্দ্রতা $RH = 44.28\%$</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5270,7 +4996,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>গ্যাসের অণুর আরএমএস বেগ (সমস্যা 32)</t>
+          <t>আর্দ্রতা, শিশিরাংক ও গ্লেইশারের সূত্র (Humidity, Dew Point &amp; Glaisher Formula)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5283,30 +5009,25 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>[সমস্যা 32: গ্যাসের অণুর আরএমএস বেগ]
-##PRESET:maxwell-distribution[size:medium]##
-$47^\circ\text{C}$ তাপমাত্রায় নাইট্রোজেন ($N_2$) গ্যাসের অণুর মূল গড় বর্গবেগ ($c_{rms} = \sqrt{\frac{3RT}{M}}$) কত নির্ণয় কর। ($R = 8.314\text{ J/(mol}\cdot\text{K)}, M = 28 \times 10^{-3}\text{ kg/mol}$)</t>
+          <t>##GEO:rect[w=3,h=5][size:small]##
+একটি ঘরের শুষ্ক ও আর্দ্র বাল্ব হাইগ্রোমিটারে শুষ্ক বাল্বের পাঠ $\theta = 30^\circ\text{C}$ এবং আর্দ্র বাল্বের পাঠ $\theta_w = 22^\circ\text{C}$। $30^\circ\text{C}$-এ গ্লেইশারের উৎপাদক $G = 1.65$। $16^\circ\text{C}, 17^\circ\text{C}$ ও $30^\circ\text{C}$ তাপমাত্রায় সম্পৃক্ত বাষ্পচাপ যথাক্রমে $13.63\text{ mm-Hg}, 14.53\text{ mm-Hg}$ এবং $31.82\text{ mm-Hg}$। ঘরের আপেক্ষিক আর্দ্রতা নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>##PRESET:maxwell-distribution[size:medium]##</t>
+          <t>##GEO:rect[w=3,h=5][size:small]##</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 32)।</t>
+          <t>গ্লেইশারের সূত্র: $\theta - \theta_d = G(\theta - \theta_w) \implies 30 - \theta_d = 1.65(30 - 22) = 1.65(8) = 13.2 \implies \theta_d = 30 - 13.2 = 16.8^\circ\text{C}$। $16.8^\circ\text{C}$-এ বাষ্পচাপ $f = 13.63 + 0.8(14.53 - 13.63) = 13.63 + 0.8(0.90) = 13.63 + 0.72 = 14.35\text{ mm-Hg}$। আপেক্ষিক আর্দ্রতা $RH = \frac{f}{F} \times 100\% = \frac{14.35}{31.82} \times 100\% \approx 45.097\% \approx 45.10\%$।</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 32</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>শিশিরাংক $\theta_d = 16.8^\circ\text{C}$, আপেক্ষিক আর্দ্রতা $RH = 45.10\%$</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5326,38 +5047,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>আপেক্ষিক আর্দ্রতা ও শিশিরাংক (সমস্যা 33)</t>
+          <t>আর্দ্রতা, শিশিরাংক ও গ্লেইশারের সূত্র (Humidity, Dew Point &amp; Glaisher Formula)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>[সমস্যা 33: আপেক্ষিক আর্দ্রতা ও শিশিরাংক]
-কোনো একদিন বায়ুর তাপমাত্রা $50^\circ\text{C}$ এবং শিশিরাংক $9^\circ\text{C}$। $9^\circ\text{C}$ ও $50^\circ\text{C}$-এ সম্পৃক্ত জলীয় বাষ্পের চাপ যথাক্রমে $9.2\text{ mm-Hg}$ এবং $17.5\text{ mm-Hg}$ হলে ঐ দিনের আপেক্ষিক আর্দ্রতা কত?</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+কোনো স্থানে বায়ুর তাপমাত্রা $28^\circ\text{C}$ এবং আপেক্ষিক আর্দ্রতা $65\%$। $28^\circ\text{C}$ তাপমাত্রায় সম্পৃক্ত জলীয় বাষ্পচাপ $28.35\text{ mm-Hg}$ হলে বায়ুতে উপস্থিত প্রকৃত জলীয় বাষ্পচাপ $f$ কত? ওই স্থানে শিশিরাংক কোন বাষ্পচাপের সমতুল্য?</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 33)।</t>
+          <t>$RH = \frac{f}{F} \times 100\% \implies f = \frac{RH \times F}{100} = \frac{65 \times 28.35}{100} = 18.4275\text{ mm-Hg} \approx 18.43\text{ mm-Hg}$। সংজ্ঞানুযায়ী শিশিরাংক হলো সেই তাপমাত্রা যাতে এই $18.43\text{ mm-Hg}$ বাষ্পচাপই সম্পৃক্ত বাষ্পচাপ হিসেবে কাজ করে।</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 33</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>প্রকৃত বাষ্পচাপ $f = 18.43\text{ mm-Hg}$ (শিশিরাংকের সম্পৃক্ত বাষ্পচাপের সমান)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5377,7 +5098,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>গ্যাসের মোট গতিশক্তি ও চাপ (সমস্যা 34)</t>
+          <t>আর্দ্রতা, শিশিরাংক ও গ্লেইশারের সূত্র (Humidity, Dew Point &amp; Glaisher Formula)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5390,25 +5111,25 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>[সমস্যা 34: গ্যাসের মোট গতিশক্তি ও চাপ]
-একটি $V = 6\text{ m}^3$ আয়তনের পাত্রে $P = 11 \times 10^5\text{ Pa}$ চাপে গ্যাস আবদ্ধ আছে। পাত্রে রক্ষিত সমগ্র গ্যাসের মোট গতিশক্তি ($E_k = \frac{3}{2}PV$) কত জুল?</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি $5.0\text{ m} 	imes 4.0\text{ m} 	imes 3.0\text{ m}$ আয়তনের ঘরের তাপমাত্রা $20^\circ\text{C}$ এবং আপেক্ষিক আর্দ্রতা $60\%$। $20^\circ\text{C}$ তাপমাত্রায় সম্পৃক্ত বাষ্পের ঘনত্ব $17.3\text{ g/m}^3$। ওই ঘরে উপস্থিত মোট জলীয় বাষ্পের ভর কত কেজি?</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 34)।</t>
+          <t>ঘরের আয়তন $V = 5 \times 4 \times 3 = 60.0\text{ m}^3$। সম্পৃক্ত অবস্থায় প্রতি ঘনমিটারে সর্বোচ্চ বাষ্প থাকতে পারে $\rho_{\text{sat}} = 17.3\text{ g/m}^3$। $60\%$ আর্দ্রতায় প্রকৃত ঘনত্ব $\rho = 0.60 \times 17.3 = 10.38\text{ g/m}^3$। মোট জলীয় বাষ্পের ভর $m = V \times \rho = 60 \times 10.38 = 622.8\text{ g} \approx 0.623\text{ kg}$।</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 34</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>জলীয় বাষ্পের ভর $m = 0.623\text{ kg} = 622.8\text{ g}$</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5428,38 +5149,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>স্বাধীনতার মাত্রা ও মোলার তাপধারণ ক্ষমতা (সমস্যা 35)</t>
+          <t>আর্দ্রতা, শিশিরাংক ও গ্লেইশারের সূত্র (Humidity, Dew Point &amp; Glaisher Formula)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>[সমস্যা 35: স্বাধীনতার মাত্রা ও মোলার তাপধারণ ক্ষমতা]
-একটি দ্বি-পরমাণুক আদর্শ গ্যাসের স্বাধীনতার মাত্রা $f = 5$ হলে গ্যাসটির স্থির চাপে ও স্থির আয়তনে মোলার আপেক্ষিক তাপদ্বয়ের অনুপাত $\gamma = C_p / C_v$ কত?</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##
+একটি কাচের গ্লাসে বরফ কুচি রাখায় গ্লাসের বহির্গাত্রে যখন প্রথম জলকণা জমতে শুরু করল তখন গ্লাসের তাপমাত্রা ছিল $10^\circ\text{C}$। ওই সময় ঘরের তাপমাত্রা ছিল $24^\circ\text{C}$। $10^\circ\text{C}$ ও $24^\circ\text{C}$-এ সম্পৃক্ত বাষ্পচাপ যথাক্রমে $9.21\text{ mm-Hg}$ এবং $22.38\text{ mm-Hg}$ হলে ঘরের আপেক্ষিক আর্দ্রতা কত?</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 35)।</t>
+          <t>বহির্গাত্রে জলকণা জমার তাপমাত্রা হলো শিশিরাংক, সুতরাং শিশিরাংক $\theta_d = 10^\circ\text{C}$। বায়ুর তাপমাত্রা $\theta = 24^\circ\text{C}$। শিশিরাংকে সম্পৃক্ত বাষ্পচাপ $f = 9.21\text{ mm-Hg}$ এবং বায়ুর তাপমাত্রায় সম্পৃক্ত বাষ্পচাপ $F = 22.38\text{ mm-Hg}$। $RH = \frac{f}{F} \times 100\% = \frac{9.21}{22.38} \times 100\% \approx 41.15\%$।</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 35</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>আপেক্ষিক আর্দ্রতা $RH = 41.15\%$</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5479,7 +5200,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>গ্যাসের ব্যাপন ও গ্রাহামের সূত্র (সমস্যা 36)</t>
+          <t>আর্দ্রতা, শিশিরাংক ও গ্লেইশারের সূত্র (Humidity, Dew Point &amp; Glaisher Formula)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5492,25 +5213,25 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>[সমস্যা 36: গ্যাসের ব্যাপন ও গ্রাহামের সূত্র]
-একই তাপমাত্রা ও চাপে একটি সরু ছিদ্র দিয়ে অক্সিজেন গ্যাসের ব্যাপিত হতে $20\text{ s}$ সময় লাগে। সম-আয়তনের একটি অজানা গ্যাসের ব্যাপিত হতে $50\text{ s}$ সময় লাগলে অজানা গ্যাসটির আণবিক ভর কত?</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি নির্দিষ্ট আয়তনের আবদ্ধ কক্ষে $30^\circ\text{C}$ তাপমাত্রায় আপেক্ষিক আর্দ্রতা $50\%$। কক্ষটির তাপমাত্রা কমিয়ে কত করা হলে বাষ্প ঘনীভূত হয়ে শিশির জমতে শুরু করবে? ($30^\circ\text{C}$-এ সম্পৃক্ত চাপ $31.8\text{ mm-Hg}$, এবং $15^\circ\text{C}, 18^\circ\text{C}, 20^\circ\text{C}$-এ সম্পৃক্ত চাপ যথাক্রমে $12.8\text{ mm-Hg}, 15.5\text{ mm-Hg}, 17.5\text{ mm-Hg}$)।</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 36)।</t>
+          <t>প্রকৃত জলীয় বাষ্পচাপ $f = 0.50 \times 31.8 = 15.9\text{ mm-Hg}$। তাপমাত্রা কমালে যতক্ষণ না এই $15.9\text{ mm-Hg}$ সম্পৃক্ত মানে পরিণত হয় ততক্ষণ শিশির জমবে না। $18^\circ\text{C}$-এ চাপ $15.5\text{ mm-Hg}$ এবং $20^\circ\text{C}$-এ $17.5\text{ mm-Hg}$। ইন্টারপোলেশন করে: $\theta_d \approx 18 + \frac{15.9 - 15.5}{17.5 - 15.5}(2) = 18 + \frac{0.4}{2.0}(2) = 18.4^\circ\text{C}$।</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 36</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>শিশির জমার তাপমাত্রা (শিশিরাংক) $\approx 18.4^\circ\text{C}$</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5530,38 +5251,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>গ্যাসের গড় মুক্ত পথ (সমস্যা 37)</t>
+          <t>আর্দ্রতা, শিশিরাংক ও গ্লেইশারের সূত্র (Humidity, Dew Point &amp; Glaisher Formula)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>[সমস্যা 37: গ্যাসের গড় মুক্ত পথ]
-অক্সিজেন গ্যাসের অণুর ব্যাস $d = 3 \times 10^{-10}\text{ m}$ এবং প্রতি ঘনমিটারে অণুর সংখ্যা $n = 3 \times 10^{25}\text{ m}^{-3}$ হলে অণুগুলোর গড় মুক্ত পথ ($\lambda = \frac{1}{\sqrt{2}\pi n d^2}$) কত?</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+একটি ঘরে $20^\circ\text{C}$ তাপমাত্রায় আপেক্ষিক আর্দ্রতা $80\%$। যদি কোনো জলীয় বাষ্পের অপচয় না করে ঘরের তাপমাত্রা বাড়িয়ে $30^\circ\text{C}$ করা হয়, তবে নতুন আপেক্ষিক আর্দ্রতা কত হবে? ($20^\circ\text{C}$ ও $30^\circ\text{C}$-এ সম্পৃক্ত বাষ্পচাপ যথাক্রমে $17.5\text{ mm-Hg}$ ও $31.8\text{ mm-Hg}$)।</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 37)।</t>
+          <t>প্রকৃত বাষ্পচাপ $f = 0.80 \times 17.5 = 14.0\text{ mm-Hg}$ (বাষ্পের পরিমাণ স্থির থাকায় এটি স্থির থাকে)। $30^\circ\text{C}$-এ সম্পৃক্ত চাপ $F' = 31.8\text{ mm-Hg}$। নতুন আর্দ্রতা $RH' = \frac{f}{F'} \times 100\% = \frac{14.0}{31.8} \times 100\% \approx 44.025\% \approx 44.03\%$।</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 37</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>নতুন আপেক্ষিক আর্দ্রতা $RH' = 44.03\%$</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5581,7 +5302,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ভ্যান ডার ওয়ালস বাস্তব গ্যাস (সমস্যা 38)</t>
+          <t>আর্দ্রতা, শিশিরাংক ও গ্লেইশারের সূত্র (Humidity, Dew Point &amp; Glaisher Formula)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5594,25 +5315,25 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>[সমস্যা 38: ভ্যান ডার ওয়ালস বাস্তব গ্যাস]
-$1\text{ mol}$ কার্বন ডাই-অক্সাইড গ্যাসের জন্য ভ্যান ডার ওয়ালস ধ্রুবক $a = 0.36\text{ N}\cdot\text{m}^4/\text{mol}^2$ এবং $b = 4.3 \times 10^{-5}\text{ m}^3/\text{mol}$ হলে এর মাত্রাগত তাৎপর্য ব্যাখ্যা কর।</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+বর্ষাকালে একদিন বায়ুর তাপমাত্রা $30^\circ\text{C}$ এবং আপেক্ষিক আর্দ্রতা $90\%$। শীতকালে তাপমাত্রা কমে $15^\circ\text{C}$ এবং আপেক্ষিক আর্দ্রতা $60\%$ হলো। উভয় ক্ষেত্রে বাতাসের প্রকৃত বাষ্পচাপের অনুপাত কত? ($30^\circ\text{C}$ ও $15^\circ\text{C}$-এ সম্পৃক্ত চাপ যথাক্রমে $31.8\text{ mm-Hg}$ এবং $12.8\text{ mm-Hg}$)।</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 38)।</t>
+          <t>১ম ক্ষেত্রে প্রকৃত চাপ $f_1 = 0.90 \times 31.8 = 28.62\text{ mm-Hg}$। ২য় ক্ষেত্রে প্রকৃত চাপ $f_2 = 0.60 \times 12.8 = 7.68\text{ mm-Hg}$। অনুপাত $\frac{f_1}{f_2} = \frac{28.62}{7.68} \approx 3.7265 \approx 3.73$।</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 38</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>অনুপাত $f_1 : f_2 = 3.73 : 1$</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5632,38 +5353,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>মিশ্র গ্যাসের মোট চাপ (ডাল্টনের সূত্র) (সমস্যা 39)</t>
+          <t>আর্দ্রতা, শিশিরাংক ও গ্লেইশারের সূত্র (Humidity, Dew Point &amp; Glaisher Formula)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>[সমস্যা 39: মিশ্র গ্যাসের মোট চাপ (ডাল্টনের সূত্র)]
-$V_1 = 2\text{ L}$ আয়তনের পাত্রে $P_1 = 5\text{ atm}$ চাপে অক্সিজেন এবং $V_2 = 3\text{ L}$ আয়তনের পাত্রে $P_2 = 11\text{ atm}$ চাপে নাইট্রোজেন গ্যাস নিয়ে যুক্ত করলে মিশ্রণের মোট চাপ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>##GEO:rect[w=3,h=5][size:small]##
+একটি আবহাওয়া পর্যবেক্ষণ কেন্দ্রে শুষ্ক বাল্বের পাঠ $24^\circ\text{C}$ এবং আর্দ্র বাল্বের পাঠ $18^\circ\text{C}$। গ্লেইশারের উৎপাদক $G = 1.70$। $13^\circ\text{C}$ ও $14^\circ\text{C}$-এ সম্পৃক্ত বাষ্পচাপ যথাক্রমে $11.23\text{ mm-Hg}$ এবং $11.99\text{ mm-Hg}$, এবং $24^\circ\text{C}$-এ $22.38\text{ mm-Hg}$। আপেক্ষিক আর্দ্রতা নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=3,h=5][size:small]##</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 39)।</t>
+          <t>শিশিরাংক $\theta_d = 24 - 1.70(24 - 18) = 24 - 1.70(6) = 24 - 10.2 = 13.8^\circ\text{C}$। $13.8^\circ\text{C}$-এ চাপ $f = 11.23 + 0.8(11.99 - 11.23) = 11.23 + 0.8(0.76) = 11.23 + 0.608 = 11.838\text{ mm-Hg}$। আর্দ্রতা $RH = \frac{11.838}{22.38} \times 100\% \approx 52.895\% \approx 52.90\%$।</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 39</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>শিশিরাংক $\theta_d = 13.8^\circ\text{C}$, আপেক্ষিক আর্দ্রতা $RH = 52.90\%$</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5683,7 +5404,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>পরম শূন্য তাপমাত্রা ও গ্যাস সিলিন্ডার (সমস্যা 40)</t>
+          <t>আর্দ্রতা, শিশিরাংক ও গ্লেইশারের সূত্র (Humidity, Dew Point &amp; Glaisher Formula)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5696,25 +5417,25 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>[সমস্যা 40: পরম শূন্য তাপমাত্রা ও গ্যাস সিলিন্ডার]
-একটি স্টিল সিলিন্ডারে $67^\circ\text{C}$ তাপমাত্রায় $P = 3\text{ atm}$ চাপে গ্যাস রক্ষিত আছে। তাপমাত্রা বৃদ্ধি পেয়ে $127^\circ\text{C}$ হলে সিলিন্ডারের অভ্যন্তরীণ চাপ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+সম্পৃক্ত বাষ্পচাপের বৈশিষ্ট্য: একটি আবদ্ধ সিলিন্ডারে পিস্টন দ্বারা সম্পৃক্ত জলীয় বাষ্পকে সংকুচিত করে আয়তন অর্ধেক করা হলো (তাপমাত্রা স্থির)। বাষ্পচাপের কী পরিবর্তন হবে এবং বাষ্পের কী ঘটবে ব্যাখ্যা কর।</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 40)।</t>
+          <t>নির্দিষ্ট তাপমাত্রায় সম্পৃক্ত বাষ্প বয়েলের সূত্র মেনে চলে না; এর চাপ কেবল তাপমাত্রার ওপর নির্ভরশীল ধ্রুব রাশি $P_{\text{sat}}$। আয়তন অর্ধেক করা হলে অতিরিক্ত বাষ্প ঘনীভূত হয়ে পানিতে রূপান্তরিত হয় যাতে অবশিষ্ট বাষ্পের ঘনত্ব এবং চাপ উভয়ই সম্পৃক্ত মানে স্থির থাকে।</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 40</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+          <t>চাপ অপরিবর্তিত থাকবে ($P' = P_{\text{sat}}$), বাষ্পের অর্ধেক অংশ ঘনীভূত হয়ে তরলে পরিণত হবে</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5734,43 +5455,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>হ্রদের গভীরতা ও বুদবুদ প্রসারণ (সমস্যা 41)</t>
+          <t>বাস্তব গ্যাস, ভ্যান ডার ওয়ালস ও তাপগতিবিদ্যা (Real Gas &amp; Van der Waals)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>[সমস্যা 41: হ্রদের গভীরতা ও বুদবুদ প্রসারণ]
-##PRESET:pv-diagram(isothermal)[size:medium]##
-একটি হ্রদের তলদেশ হতে একটি বায়ুর বুদবুদ পানির উপরিপৃষ্ঠে উঠে আসায় এর আয়তন 7 গুণ হয়। বায়ুমণ্ডলীয় চাপ $1.013 \times 10^5\text{ Pa}$, পানির ঘনত্ব $1000\text{ kg/m}^3$, এবং তাপমাত্রা ধ্রুব থাকলে হ্রদের গভীরতা কত? ($g = 9.8\text{ m/s}^2$)</t>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+১ মোল বাস্তব গ্যাসের জন্য ভ্যান ডার ওয়ালস সমীকরণ $\left(P + \frac{a}{V_m^2}\right)(V_m - b) = RT$। এখানে ধ্রুবক $a$ এবং $b$ বাস্তব গ্যাসের কোন কোন আণবিক ত্রুটির সংশোধন নির্দেশ করে এবং এদের এসআই একক কী?</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>##PRESET:pv-diagram(isothermal)[size:medium]##</t>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 41)।</t>
+          <t>$a/V_m^2$ পদটি আন্তঃআণবিক আকর্ষণজনিত অভ্যন্তরীণ চাপ (Cohesion pressure) সংশোধন করে, এর একক $\frac{P}{1/V^2} = \text{Pa}\cdot(\text{m}^3/\text{mol})^2 = \text{Pa}\cdot\text{m}^6/\text{mol}^2$। $b$ হলো ৪ গুণ আণবিক আয়তনের সমতুল্য কো-ভলিউম (Excluded volume), এর একক $\text{m}^3/\text{mol}$।</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 41</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>$a$-এর একক $\text{N}\cdot\text{m}^4/\text{mol}^2$ বা $\text{Pa}\cdot\text{m}^6/\text{mol}^2$ (আণবিক আকর্ষণ বল), $b$-এর একক $\text{m}^3/\text{mol}$ (অণুগুলোর নিজস্ব কার্যকর আয়তন)</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5790,12 +5506,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>গ্যাসের অণুর আরএমএস বেগ (সমস্যা 42)</t>
+          <t>বাস্তব গ্যাস, ভ্যান ডার ওয়ালস ও তাপগতিবিদ্যা (Real Gas &amp; Van der Waals)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -5803,30 +5519,25 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>[সমস্যা 42: গ্যাসের অণুর আরএমএস বেগ]
-##PRESET:maxwell-distribution[size:medium]##
-$27^\circ\text{C}$ তাপমাত্রায় নাইট্রোজেন ($N_2$) গ্যাসের অণুর মূল গড় বর্গবেগ ($c_{rms} = \sqrt{\frac{3RT}{M}}$) কত নির্ণয় কর। ($R = 8.314\text{ J/(mol}\cdot\text{K)}, M = 28 \times 10^{-3}\text{ kg/mol}$)</t>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##
+একটি গ্যাস পাত্রে $T_1 = 300\text{ K}$ তাপমাত্রায় এবং $P_1 = 2.0\text{ atm}$ চাপে $1.0\text{ kg}$ বাতাস আছে। পাত্রে একটি ক্ষুদ্র ছিদ্র দিয়ে কিছু বাতাস বের হয়ে যাওয়ায় তাপমাত্রা $350\text{ K}$ করার পর চাপ কমে $1.5\text{ atm}$ হলো। পাত্র হতে কত কেজি বাতাস বের হয়ে গেছে?</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>##PRESET:maxwell-distribution[size:medium]##</t>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 42)।</t>
+          <t>আয়তন স্থির থাকায় $P \propto m T \implies \frac{P_2}{P_1} = \frac{m_2 T_2}{m_1 T_1} \implies \frac{1.5}{2.0} = \frac{m_2 \times 350}{1.0 \times 300} \implies 0.75 = \frac{35}{30}m_2 = \frac{7}{6}m_2 \implies m_2 = 0.75 \times \frac{6}{7} = \frac{4.5}{7} \approx 0.6429\text{ kg}$। বের হয়ে যাওয়া ভর $\Delta m = 1.0 - 0.6429 = 0.3571\text{ kg} \approx 357.1\text{ g}$।</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 42</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>বের হয়ে যাওয়া বাতাসের ভর $\Delta m = 0.357\text{ kg} = 357.1\text{ g}$</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5846,38 +5557,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>আপেক্ষিক আর্দ্রতা ও শিশিরাংক (সমস্যা 43)</t>
+          <t>বাস্তব গ্যাস, ভ্যান ডার ওয়ালস ও তাপগতিবিদ্যা (Real Gas &amp; Van der Waals)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>[সমস্যা 43: আপেক্ষিক আর্দ্রতা ও শিশিরাংক]
-কোনো একদিন বায়ুর তাপমাত্রা $30^\circ\text{C}$ এবং শিশিরাংক $9^\circ\text{C}$। $9^\circ\text{C}$ ও $30^\circ\text{C}$-এ সম্পৃক্ত জলীয় বাষ্পের চাপ যথাক্রমে $9.2\text{ mm-Hg}$ এবং $17.5\text{ mm-Hg}$ হলে ঐ দিনের আপেক্ষিক আর্দ্রতা কত?</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+একটি $10.0\text{ L}$ পাত্রে $27^\circ\text{C}$ তাপমাত্রায় $0.1\text{ মোল}$ জলীয় বাষ্প রয়েছে। যদি সম্পূর্ণ বাষ্প ঘনীভূত হয়ে তরল পানিতে পরিণত হয়, তবে তরল পানির আয়তন কত মিলিলিটার হবে? (পানির ঘনত্ব $1.0\text{ g/cm}^3$)। ঘনীভবনের ফলে আয়তন কত গুণ সংকুচিত হলো?</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 43)।</t>
+          <t>$0.1$ মোল পানির ভর $m = 0.1 \times 18 = 1.8\text{ g}$। তরল পানির ঘনত্ব $1.0\text{ g/mL}$ হওয়ায় তরল পানির আয়তন $V_{\text{liquid}} = 1.8\text{ mL} = 1.8 \times 10^{-6}\text{ m}^3$। আদি বাষ্পের আয়তন $10\text{ L} = 10000\text{ mL}$। আয়তন সংকোচন অনুপাত $= \frac{10000}{1.8} \approx 5555.56$ গুণ।</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 43</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+          <t>তরল পানির আয়তন $1.8\text{ mL}$, আয়তন সংকোচন প্রায় $5555$ গুণ</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5897,12 +5608,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>গ্যাসের মোট গতিশক্তি ও চাপ (সমস্যা 44)</t>
+          <t>বাস্তব গ্যাস, ভ্যান ডার ওয়ালস ও তাপগতিবিদ্যা (Real Gas &amp; Van der Waals)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -5910,25 +5621,25 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>[সমস্যা 44: গ্যাসের মোট গতিশক্তি ও চাপ]
-একটি $V = 4\text{ m}^3$ আয়তনের পাত্রে $P = 11 \times 10^5\text{ Pa}$ চাপে গ্যাস আবদ্ধ আছে। পাত্রে রক্ষিত সমগ্র গ্যাসের মোট গতিশক্তি ($E_k = \frac{3}{2}PV$) কত জুল?</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি গ্যাসের সংকট তাপমাত্রা (Critical temperature $T_c$) ও সংকট চাপ (Critical pressure $P_c$) যথাক্রমে $T_c = rac{8a}{27Rb}$ এবং $P_c = rac{a}{27b^2}$। সংকট বিন্দুতে গ্যাসের পেষণ গুণক (Critical Compressibility Factor $Z_c = rac{P_c V_c}{R T_c}$) কত? প্রমাণ কর যে এটি সকল ভ্যান ডার ওয়ালস গ্যাসের জন্য ধ্রুবক।</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 44)।</t>
+          <t>সংকট আয়তন $V_c = 3b$। মান বসিয়ে: $Z_c = \frac{P_c V_c}{R T_c} = \frac{\left(\frac{a}{27b^2}\right)(3b)}{R\left(\frac{8a}{27Rb}\right)} = \frac{\frac{3a}{27b}}{\frac{8a}{27b}} = \frac{3}{8} = 0.375$। এটি গ্যাস ধ্রুবক $a$ ও $b$-এর ওপর নির্ভর করে না, ফলে সকল বাস্তব গ্যাসের সংকট সংকোচনশীলতা ফ্যাক্টর তাত্ত্বিকভাবে $0.375$।</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 44</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>$Z_c = \frac{3}{8} = 0.375$ (সার্বজনীন ধ্রুবক)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5948,38 +5659,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>স্বাধীনতার মাত্রা ও মোলার তাপধারণ ক্ষমতা (সমস্যা 45)</t>
+          <t>বাস্তব গ্যাস, ভ্যান ডার ওয়ালস ও তাপগতিবিদ্যা (Real Gas &amp; Van der Waals)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>[সমস্যা 45: স্বাধীনতার মাত্রা ও মোলার তাপধারণ ক্ষমতা]
-একটি দ্বি-পরমাণুক আদর্শ গ্যাসের স্বাধীনতার মাত্রা $f = 5$ হলে গ্যাসটির স্থির চাপে ও স্থির আয়তনে মোলার আপেক্ষিক তাপদ্বয়ের অনুপাত $\gamma = C_p / C_v$ কত?</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2.5,h=3][size:small]##
+একটি $2.0\text{ m}^3$ পাত্রে $0.05\text{ kg}$ জলীয় বাষ্প $100^\circ\text{C}$ তাপমাত্রায় সম্পৃক্ত অবস্থায় রাখা আছে। বাষ্পটির চাপ আদর্শ গ্যাস সমীকরণ দ্বারা নির্ণয় কর এবং বাস্তব বায়ুমণ্ডলীয় চাপের ($1.013 \times 10^5\text{ Pa}$) সাথে তুলনা কর। ($M = 18\text{ g/mol}$)।</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2.5,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 45)।</t>
+          <t>মোল সংখ্যা $n = \frac{m}{M} = \frac{50\text{ g}}{18\text{ g/mol}} = 2.778\text{ mol}$। তাপমাত্রা $T = 373.15\text{ K}$, আয়তন $V = 2.0\text{ m}^3$। চাপ $P = \frac{nRT}{V} = \frac{2.778 \times 8.314 \times 373.15}{2.0} = \frac{8617.9}{2.0} \approx 43089.5\text{ Pa} \approx 43.1\text{ kPa}$।</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 45</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+          <t>হিসাবকৃত চাপ $P = 43.1\text{ kPa} \approx 0.425\text{ atm}$</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5999,12 +5710,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>গ্যাসের ব্যাপন ও গ্রাহামের সূত্র (সমস্যা 46)</t>
+          <t>বাস্তব গ্যাস, ভ্যান ডার ওয়ালস ও তাপগতিবিদ্যা (Real Gas &amp; Van der Waals)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -6012,25 +5723,25 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>[সমস্যা 46: গ্যাসের ব্যাপন ও গ্রাহামের সূত্র]
-একই তাপমাত্রা ও চাপে একটি সরু ছিদ্র দিয়ে অক্সিজেন গ্যাসের ব্যাপিত হতে $60\text{ s}$ সময় লাগে। সম-আয়তনের একটি অজানা গ্যাসের ব্যাপিত হতে $50\text{ s}$ সময় লাগলে অজানা গ্যাসটির আণবিক ভর কত?</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+বয়েল তাপমাত্রা ($T_B = rac{a}{Rb}$) বলতে কী বোঝায়? নাইট্রোজেন গ্যাসের জন্য $a = 0.1408\text{ Pa}\cdot\text{m}^6/\text{mol}^2$ এবং $b = 3.91 \times 10^{-5}\text{ m}^3/\text{mol}$ হলে নাইট্রোজেনের বয়েল তাপমাত্রা কত কেলভিন?</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 46)।</t>
+          <t>যে তাপমাত্রায় বাস্তব গ্যাস বিস্তৃত চাপ পরিসরে বয়েলের সূত্র নিখুঁতভাবে মেনে চলে তাকে বয়েল তাপমাত্রা বলে। $T_B = \frac{a}{R b} = \frac{0.1408}{8.314 \times 3.91 \times 10^{-5}} = \frac{0.1408}{3.2508 \times 10^{-4}} \approx 433.12\text{ K}$। সেলসিয়াসে $\theta_B = 433.12 - 273.15 = 159.97^\circ\text{C} \approx 160.0^\circ\text{C}$।</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 46</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+          <t>বয়েল তাপমাত্রা $T_B = 433.1\text{ K} = 160.1^\circ\text{C}$</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6050,38 +5761,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>গ্যাসের গড় মুক্ত পথ (সমস্যা 47)</t>
+          <t>বাস্তব গ্যাস, ভ্যান ডার ওয়ালস ও তাপগতিবিদ্যা (Real Gas &amp; Van der Waals)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>[সমস্যা 47: গ্যাসের গড় মুক্ত পথ]
-অক্সিজেন গ্যাসের অণুর ব্যাস $d = 3 \times 10^{-10}\text{ m}$ এবং প্রতি ঘনমিটারে অণুর সংখ্যা $n = 7 \times 10^{25}\text{ m}^{-3}$ হলে অণুগুলোর গড় মুক্ত পথ ($\lambda = \frac{1}{\sqrt{2}\pi n d^2}$) কত?</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##
+একটি আদর্শ গ্যাসের $1\text{ মোল}$ সমোষ্ণ প্রক্রিয়ায় $V_1 = 1.0\text{ L}$ হতে প্রসারিত হয়ে $V_2 = 10.0\text{ L}$ আয়তন লাভ করল। তাপমাত্রা $300\text{ K}$ হলে গ্যাসের কৃতকাজ $W$ নির্ণয় কর। ($R = 8.314\text{ J/mol}\cdot\text{K}$)।</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 47)।</t>
+          <t>সমোষ্ণ প্রসারণে কৃতকাজ $W = nRT\ln\left(\frac{V_2}{V_1}\right) = 1.0 \times 8.314 \times 300 \times \ln(10) = 2494.2 \times 2.302585 \approx 5743.1\text{ J} = 5.743\text{ kJ}$।</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 47</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>কৃতকাজ $W = 5743.1\text{ J} = 5.74\text{ kJ}$</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6101,12 +5812,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ভ্যান ডার ওয়ালস বাস্তব গ্যাস (সমস্যা 48)</t>
+          <t>বাস্তব গ্যাস, ভ্যান ডার ওয়ালস ও তাপগতিবিদ্যা (Real Gas &amp; Van der Waals)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -6114,25 +5825,25 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>[সমস্যা 48: ভ্যান ডার ওয়ালস বাস্তব গ্যাস]
-$1\text{ mol}$ কার্বন ডাই-অক্সাইড গ্যাসের জন্য ভ্যান ডার ওয়ালস ধ্রুবক $a = 0.36\text{ N}\cdot\text{m}^4/\text{mol}^2$ এবং $b = 4.3 \times 10^{-5}\text{ m}^3/\text{mol}$ হলে এর মাত্রাগত তাৎপর্য ব্যাখ্যা কর।</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+একটি দ্বিপরমাণুক গ্যাসের মোলার তাপধারণ ক্ষমতা স্থির চাপে $C_p$ এবং স্থির আয়তনে $C_v$। দেখাও যে কম্পন মোড অনুপস্থিত থাকলে $\gamma = C_p/C_v = 1.40$ এবং স্থির আয়তনে ১ মোলের অভ্যন্তরীণ শক্তি বৃদ্ধি $\Delta U = C_v \Delta T$।</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 48)।</t>
+          <t>স্বাধীনতার মাত্রা $f = 5$ (৩টি স্থানান্তরীয় + ২টি ঘূর্ণন)। $C_v = \frac{f}{2}R = \frac{5}{2}R = 2.5(8.314) = 20.785\text{ J/mol}\cdot\text{K}$। মেয়ারের সূত্র অনুসারে $C_p = C_v + R = \frac{7}{2}R = 3.5(8.314) = 29.099\text{ J/mol}\cdot\text{K}$। অনুপাত $\gamma = \frac{C_p}{C_v} = \frac{7}{5} = 1.40$।</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 48</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>$\gamma = \frac{7/2 R}{5/2 R} = 1.40$, $C_v = \frac{5}{2}R \approx 20.785\text{ J/mol}\cdot\text{K}$</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6152,38 +5863,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>মিশ্র গ্যাসের মোট চাপ (ডাল্টনের সূত্র) (সমস্যা 49)</t>
+          <t>বাস্তব গ্যাস, ভ্যান ডার ওয়ালস ও তাপগতিবিদ্যা (Real Gas &amp; Van der Waals)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>[সমস্যা 49: মিশ্র গ্যাসের মোট চাপ (ডাল্টনের সূত্র)]
-$V_1 = 2\text{ L}$ আয়তনের পাত্রে $P_1 = 3\text{ atm}$ চাপে অক্সিজেন এবং $V_2 = 3\text{ L}$ আয়তনের পাত্রে $P_2 = 11\text{ atm}$ চাপে নাইট্রোজেন গ্যাস নিয়ে যুক্ত করলে মিশ্রণের মোট চাপ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+একটি সিলিন্ডারে রক্ষিত বাতাসের চাপ $10\text{ atm}$ এবং আয়তন $50\text{ L}$। সিলিন্ডারটি ফুটো হয়ে যাওয়ায় বায়ুমণ্ডলে ($1\text{ atm}$) বাতাস ছড়িয়ে পড়ল। সমস্ত বাতাস বায়ুমণ্ডলীয় চাপে এলে তার প্রসারিত মোট আয়তন কত লিটার হবে? (তাপমাত্রা অপরিবর্তিত)।</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 49)।</t>
+          <t>বয়েলের সূত্র অনুসারে $P_1 V_1 = P_2 V_2 \implies V_2 = V_1\frac{P_1}{P_2} = 50 \times \frac{10}{1} = 500.0\text{ L}$।</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 49</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>প্রসারিত মোট আয়তন $V_2 = 500.0\text{ L}$</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6203,12 +5914,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>পরম শূন্য তাপমাত্রা ও গ্যাস সিলিন্ডার (সমস্যা 50)</t>
+          <t>বাস্তব গ্যাস, ভ্যান ডার ওয়ালস ও তাপগতিবিদ্যা (Real Gas &amp; Van der Waals)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -6216,25 +5927,25 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>[সমস্যা 50: পরম শূন্য তাপমাত্রা ও গ্যাস সিলিন্ডার]
-একটি স্টিল সিলিন্ডারে $47^\circ\text{C}$ তাপমাত্রায় $P = 3\text{ atm}$ চাপে গ্যাস রক্ষিত আছে। তাপমাত্রা বৃদ্ধি পেয়ে $147^\circ\text{C}$ হলে সিলিন্ডারের অভ্যন্তরীণ চাপ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+ডাল্টনের আংশিক চাপ সূত্রের সীমাবদ্ধতা: কখন ডাল্টনের সূত্র কার্যকরভাবে প্রযোজ্য হয় এবং কেন রাসায়নিকভাবে বিক্রিয়াশীল গ্যাস মিশ্রণের ক্ষেত্রে এটি প্রযোজ্য নয় ব্যাখ্যা কর।</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>আদর্শ গ্যাস সূত্রাবলি, গতিতত্ত্বের মূল স্বীকার্য এবং বায়ুমণ্ডলীয় আর্দ্রতার সমীকরণ দ্বারা সমাধান (সমস্যা 50)।</t>
+          <t>ডাল্টনের সূত্র কেবল তখনই প্রযোজ্য যখন গ্যাস মিশ্রণের উপাদানগুলো পরস্পরের সাথে রাসায়নিক বিক্রিয়ায় লিপ্ত হয় না (যেমন $\text{O}_2$ ও $\text{N}_2$)। যদি গ্যাসগুলো বিক্রিয়া করে (যেমন $\text{NH}_3$ ও $\text{HCl}$ বা $\text{NO}$ ও $\text{O}_2$), তবে গ্যাস অণুর মোট সংখ্যা হ্রাস বা বৃদ্ধি পায় এবং নতুন পদার্থ উৎপন্ন হওয়ায় ডাল্টনের সূত্রের মূল ভিত্তি $P = \sum P_i$ লঙ্ঘিত হয়।</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>গ্যাসের গতিতত্ত্বের উত্তর 50</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>কেবলমাত্র রাসায়নিকভাবে নিষ্ক্রিয় গ্যাস মিশ্রণে প্রযোজ্য; বিক্রিয়া ঘটলে মোল সংখ্যা পরিবর্তিত হয়</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
